--- a/Test_Results/Android/android-report.xlsx
+++ b/Test_Results/Android/android-report.xlsx
@@ -7441,7 +7441,7 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -7800,7 +7800,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -33400,6 +33400,6 @@
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Test_Results/Android/android-report.xlsx
+++ b/Test_Results/Android/android-report.xlsx
@@ -33,7 +33,7 @@
     <t>Run Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:37:04.534Z</t>
+    <t>2026-07-24T14:31:03.413Z</t>
   </si>
   <si>
     <t>CI Run #</t>
@@ -72,7 +72,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>23073ms</t>
+    <t>23157ms</t>
   </si>
   <si>
     <t>Categories</t>
@@ -7441,7 +7441,7 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -7509,7 +7509,7 @@
         <v>31</v>
       </c>
       <c r="H2" s="6">
-        <v>2115</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7535,7 +7535,7 @@
         <v>31</v>
       </c>
       <c r="H3" s="8">
-        <v>2131</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7561,7 +7561,7 @@
         <v>31</v>
       </c>
       <c r="H4" s="6">
-        <v>2052</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7587,7 +7587,7 @@
         <v>31</v>
       </c>
       <c r="H5" s="8">
-        <v>2120</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7613,7 +7613,7 @@
         <v>31</v>
       </c>
       <c r="H6" s="6">
-        <v>2077</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7639,7 +7639,7 @@
         <v>31</v>
       </c>
       <c r="H7" s="8">
-        <v>2025</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7665,7 +7665,7 @@
         <v>31</v>
       </c>
       <c r="H8" s="6">
-        <v>2102</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7691,7 +7691,7 @@
         <v>31</v>
       </c>
       <c r="H9" s="8">
-        <v>2138</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7717,7 +7717,7 @@
         <v>31</v>
       </c>
       <c r="H10" s="6">
-        <v>1978</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7743,7 +7743,7 @@
         <v>31</v>
       </c>
       <c r="H11" s="8">
-        <v>2156</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7769,7 +7769,7 @@
         <v>31</v>
       </c>
       <c r="H12" s="6">
-        <v>2179</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -7795,12 +7795,12 @@
         <v>17</v>
       </c>
       <c r="H13" s="10">
-        <v>23073</v>
+        <v>23157</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -7861,7 +7861,7 @@
         <v>49</v>
       </c>
       <c r="F2" s="6">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>11</v>
@@ -7884,7 +7884,7 @@
         <v>49</v>
       </c>
       <c r="F3" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>11</v>
@@ -7930,7 +7930,7 @@
         <v>49</v>
       </c>
       <c r="F5" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>11</v>
@@ -7953,7 +7953,7 @@
         <v>49</v>
       </c>
       <c r="F6" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>11</v>
@@ -7976,7 +7976,7 @@
         <v>49</v>
       </c>
       <c r="F7" s="8">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>11</v>
@@ -8022,7 +8022,7 @@
         <v>49</v>
       </c>
       <c r="F9" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>11</v>
@@ -8045,7 +8045,7 @@
         <v>49</v>
       </c>
       <c r="F10" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>11</v>
@@ -8068,7 +8068,7 @@
         <v>49</v>
       </c>
       <c r="F11" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>11</v>
@@ -8091,7 +8091,7 @@
         <v>49</v>
       </c>
       <c r="F12" s="6">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>11</v>
@@ -8114,7 +8114,7 @@
         <v>49</v>
       </c>
       <c r="F13" s="8">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>11</v>
@@ -8137,7 +8137,7 @@
         <v>49</v>
       </c>
       <c r="F14" s="6">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>11</v>
@@ -8160,7 +8160,7 @@
         <v>49</v>
       </c>
       <c r="F15" s="8">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>11</v>
@@ -8183,7 +8183,7 @@
         <v>49</v>
       </c>
       <c r="F16" s="6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>11</v>
@@ -8206,7 +8206,7 @@
         <v>49</v>
       </c>
       <c r="F17" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>11</v>
@@ -8229,7 +8229,7 @@
         <v>49</v>
       </c>
       <c r="F18" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>11</v>
@@ -8252,7 +8252,7 @@
         <v>49</v>
       </c>
       <c r="F19" s="8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>11</v>
@@ -8275,7 +8275,7 @@
         <v>49</v>
       </c>
       <c r="F20" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>11</v>
@@ -8298,7 +8298,7 @@
         <v>49</v>
       </c>
       <c r="F21" s="8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>11</v>
@@ -8321,7 +8321,7 @@
         <v>49</v>
       </c>
       <c r="F22" s="6">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>11</v>
@@ -8344,7 +8344,7 @@
         <v>49</v>
       </c>
       <c r="F23" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>11</v>
@@ -8367,7 +8367,7 @@
         <v>49</v>
       </c>
       <c r="F24" s="6">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>11</v>
@@ -8413,7 +8413,7 @@
         <v>49</v>
       </c>
       <c r="F26" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>11</v>
@@ -8436,7 +8436,7 @@
         <v>49</v>
       </c>
       <c r="F27" s="8">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>11</v>
@@ -8459,7 +8459,7 @@
         <v>49</v>
       </c>
       <c r="F28" s="6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>11</v>
@@ -8482,7 +8482,7 @@
         <v>49</v>
       </c>
       <c r="F29" s="8">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>11</v>
@@ -8505,7 +8505,7 @@
         <v>49</v>
       </c>
       <c r="F30" s="6">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>11</v>
@@ -8528,7 +8528,7 @@
         <v>49</v>
       </c>
       <c r="F31" s="8">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>11</v>
@@ -8551,7 +8551,7 @@
         <v>49</v>
       </c>
       <c r="F32" s="6">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>11</v>
@@ -8574,7 +8574,7 @@
         <v>49</v>
       </c>
       <c r="F33" s="8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>11</v>
@@ -8597,7 +8597,7 @@
         <v>49</v>
       </c>
       <c r="F34" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>11</v>
@@ -8620,7 +8620,7 @@
         <v>49</v>
       </c>
       <c r="F35" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>11</v>
@@ -8643,7 +8643,7 @@
         <v>49</v>
       </c>
       <c r="F36" s="6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>11</v>
@@ -8666,7 +8666,7 @@
         <v>49</v>
       </c>
       <c r="F37" s="8">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G37" s="8" t="s">
         <v>11</v>
@@ -8689,7 +8689,7 @@
         <v>49</v>
       </c>
       <c r="F38" s="6">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>11</v>
@@ -8712,7 +8712,7 @@
         <v>49</v>
       </c>
       <c r="F39" s="8">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>11</v>
@@ -8735,7 +8735,7 @@
         <v>49</v>
       </c>
       <c r="F40" s="6">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>11</v>
@@ -8758,7 +8758,7 @@
         <v>49</v>
       </c>
       <c r="F41" s="8">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>11</v>
@@ -8781,7 +8781,7 @@
         <v>49</v>
       </c>
       <c r="F42" s="6">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>11</v>
@@ -8804,7 +8804,7 @@
         <v>49</v>
       </c>
       <c r="F43" s="8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G43" s="8" t="s">
         <v>11</v>
@@ -8827,7 +8827,7 @@
         <v>49</v>
       </c>
       <c r="F44" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>11</v>
@@ -8850,7 +8850,7 @@
         <v>49</v>
       </c>
       <c r="F45" s="8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G45" s="8" t="s">
         <v>11</v>
@@ -8919,7 +8919,7 @@
         <v>49</v>
       </c>
       <c r="F48" s="6">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>11</v>
@@ -8942,7 +8942,7 @@
         <v>49</v>
       </c>
       <c r="F49" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G49" s="8" t="s">
         <v>11</v>
@@ -8965,7 +8965,7 @@
         <v>49</v>
       </c>
       <c r="F50" s="6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>11</v>
@@ -8988,7 +8988,7 @@
         <v>49</v>
       </c>
       <c r="F51" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G51" s="8" t="s">
         <v>11</v>
@@ -9011,7 +9011,7 @@
         <v>49</v>
       </c>
       <c r="F52" s="6">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>11</v>
@@ -9034,7 +9034,7 @@
         <v>49</v>
       </c>
       <c r="F53" s="8">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G53" s="8" t="s">
         <v>11</v>
@@ -9057,7 +9057,7 @@
         <v>49</v>
       </c>
       <c r="F54" s="6">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>11</v>
@@ -9080,7 +9080,7 @@
         <v>49</v>
       </c>
       <c r="F55" s="8">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>11</v>
@@ -9103,7 +9103,7 @@
         <v>49</v>
       </c>
       <c r="F56" s="6">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>11</v>
@@ -9126,7 +9126,7 @@
         <v>49</v>
       </c>
       <c r="F57" s="8">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G57" s="8" t="s">
         <v>11</v>
@@ -9149,7 +9149,7 @@
         <v>49</v>
       </c>
       <c r="F58" s="6">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>11</v>
@@ -9172,7 +9172,7 @@
         <v>49</v>
       </c>
       <c r="F59" s="8">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="G59" s="8" t="s">
         <v>11</v>
@@ -9195,7 +9195,7 @@
         <v>49</v>
       </c>
       <c r="F60" s="6">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>11</v>
@@ -9218,7 +9218,7 @@
         <v>49</v>
       </c>
       <c r="F61" s="8">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G61" s="8" t="s">
         <v>11</v>
@@ -9241,7 +9241,7 @@
         <v>49</v>
       </c>
       <c r="F62" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>11</v>
@@ -9264,7 +9264,7 @@
         <v>49</v>
       </c>
       <c r="F63" s="8">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G63" s="8" t="s">
         <v>11</v>
@@ -9287,7 +9287,7 @@
         <v>49</v>
       </c>
       <c r="F64" s="6">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>11</v>
@@ -9310,7 +9310,7 @@
         <v>49</v>
       </c>
       <c r="F65" s="8">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="G65" s="8" t="s">
         <v>11</v>
@@ -9333,7 +9333,7 @@
         <v>49</v>
       </c>
       <c r="F66" s="6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>11</v>
@@ -9402,7 +9402,7 @@
         <v>49</v>
       </c>
       <c r="F69" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G69" s="8" t="s">
         <v>11</v>
@@ -9425,7 +9425,7 @@
         <v>49</v>
       </c>
       <c r="F70" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>11</v>
@@ -9471,7 +9471,7 @@
         <v>49</v>
       </c>
       <c r="F72" s="6">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>11</v>
@@ -9494,7 +9494,7 @@
         <v>49</v>
       </c>
       <c r="F73" s="8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G73" s="8" t="s">
         <v>11</v>
@@ -9517,7 +9517,7 @@
         <v>49</v>
       </c>
       <c r="F74" s="6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>11</v>
@@ -9540,7 +9540,7 @@
         <v>49</v>
       </c>
       <c r="F75" s="8">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G75" s="8" t="s">
         <v>11</v>
@@ -9632,7 +9632,7 @@
         <v>49</v>
       </c>
       <c r="F79" s="8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G79" s="8" t="s">
         <v>11</v>
@@ -9655,7 +9655,7 @@
         <v>49</v>
       </c>
       <c r="F80" s="6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>11</v>
@@ -9678,7 +9678,7 @@
         <v>49</v>
       </c>
       <c r="F81" s="8">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G81" s="8" t="s">
         <v>11</v>
@@ -9724,7 +9724,7 @@
         <v>49</v>
       </c>
       <c r="F83" s="8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G83" s="8" t="s">
         <v>11</v>
@@ -9747,7 +9747,7 @@
         <v>49</v>
       </c>
       <c r="F84" s="6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G84" s="6" t="s">
         <v>11</v>
@@ -9770,7 +9770,7 @@
         <v>49</v>
       </c>
       <c r="F85" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G85" s="8" t="s">
         <v>11</v>
@@ -9793,7 +9793,7 @@
         <v>49</v>
       </c>
       <c r="F86" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G86" s="6" t="s">
         <v>11</v>
@@ -9816,7 +9816,7 @@
         <v>49</v>
       </c>
       <c r="F87" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G87" s="8" t="s">
         <v>11</v>
@@ -9862,7 +9862,7 @@
         <v>49</v>
       </c>
       <c r="F89" s="8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G89" s="8" t="s">
         <v>11</v>
@@ -9908,7 +9908,7 @@
         <v>49</v>
       </c>
       <c r="F91" s="8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G91" s="8" t="s">
         <v>11</v>
@@ -9931,7 +9931,7 @@
         <v>49</v>
       </c>
       <c r="F92" s="6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G92" s="6" t="s">
         <v>11</v>
@@ -9954,7 +9954,7 @@
         <v>49</v>
       </c>
       <c r="F93" s="8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G93" s="8" t="s">
         <v>11</v>
@@ -9977,7 +9977,7 @@
         <v>49</v>
       </c>
       <c r="F94" s="6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G94" s="6" t="s">
         <v>11</v>
@@ -10000,7 +10000,7 @@
         <v>49</v>
       </c>
       <c r="F95" s="8">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G95" s="8" t="s">
         <v>11</v>
@@ -10023,7 +10023,7 @@
         <v>49</v>
       </c>
       <c r="F96" s="6">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G96" s="6" t="s">
         <v>11</v>
@@ -10046,7 +10046,7 @@
         <v>49</v>
       </c>
       <c r="F97" s="8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G97" s="8" t="s">
         <v>11</v>
@@ -10069,7 +10069,7 @@
         <v>49</v>
       </c>
       <c r="F98" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G98" s="6" t="s">
         <v>11</v>
@@ -10092,7 +10092,7 @@
         <v>49</v>
       </c>
       <c r="F99" s="8">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G99" s="8" t="s">
         <v>11</v>
@@ -10115,7 +10115,7 @@
         <v>49</v>
       </c>
       <c r="F100" s="6">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G100" s="6" t="s">
         <v>11</v>
@@ -10138,7 +10138,7 @@
         <v>49</v>
       </c>
       <c r="F101" s="8">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G101" s="8" t="s">
         <v>11</v>
@@ -10161,7 +10161,7 @@
         <v>49</v>
       </c>
       <c r="F102" s="6">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G102" s="6" t="s">
         <v>11</v>
@@ -10184,7 +10184,7 @@
         <v>49</v>
       </c>
       <c r="F103" s="8">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G103" s="8" t="s">
         <v>11</v>
@@ -10230,7 +10230,7 @@
         <v>49</v>
       </c>
       <c r="F105" s="8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G105" s="8" t="s">
         <v>11</v>
@@ -10253,7 +10253,7 @@
         <v>49</v>
       </c>
       <c r="F106" s="6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G106" s="6" t="s">
         <v>11</v>
@@ -10299,7 +10299,7 @@
         <v>49</v>
       </c>
       <c r="F108" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G108" s="6" t="s">
         <v>11</v>
@@ -10322,7 +10322,7 @@
         <v>49</v>
       </c>
       <c r="F109" s="8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G109" s="8" t="s">
         <v>11</v>
@@ -10345,7 +10345,7 @@
         <v>49</v>
       </c>
       <c r="F110" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G110" s="6" t="s">
         <v>11</v>
@@ -10368,7 +10368,7 @@
         <v>49</v>
       </c>
       <c r="F111" s="8">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G111" s="8" t="s">
         <v>11</v>
@@ -10391,7 +10391,7 @@
         <v>49</v>
       </c>
       <c r="F112" s="6">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="G112" s="6" t="s">
         <v>11</v>
@@ -10414,7 +10414,7 @@
         <v>49</v>
       </c>
       <c r="F113" s="8">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G113" s="8" t="s">
         <v>11</v>
@@ -10460,7 +10460,7 @@
         <v>49</v>
       </c>
       <c r="F115" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G115" s="8" t="s">
         <v>11</v>
@@ -10483,7 +10483,7 @@
         <v>49</v>
       </c>
       <c r="F116" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G116" s="6" t="s">
         <v>11</v>
@@ -10506,7 +10506,7 @@
         <v>49</v>
       </c>
       <c r="F117" s="8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G117" s="8" t="s">
         <v>11</v>
@@ -10529,7 +10529,7 @@
         <v>49</v>
       </c>
       <c r="F118" s="6">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G118" s="6" t="s">
         <v>11</v>
@@ -10552,7 +10552,7 @@
         <v>49</v>
       </c>
       <c r="F119" s="8">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G119" s="8" t="s">
         <v>11</v>
@@ -10575,7 +10575,7 @@
         <v>49</v>
       </c>
       <c r="F120" s="6">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G120" s="6" t="s">
         <v>11</v>
@@ -10598,7 +10598,7 @@
         <v>49</v>
       </c>
       <c r="F121" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G121" s="8" t="s">
         <v>11</v>
@@ -10644,7 +10644,7 @@
         <v>49</v>
       </c>
       <c r="F123" s="8">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="G123" s="8" t="s">
         <v>11</v>
@@ -10667,7 +10667,7 @@
         <v>49</v>
       </c>
       <c r="F124" s="6">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G124" s="6" t="s">
         <v>11</v>
@@ -10690,7 +10690,7 @@
         <v>49</v>
       </c>
       <c r="F125" s="8">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G125" s="8" t="s">
         <v>11</v>
@@ -10713,7 +10713,7 @@
         <v>49</v>
       </c>
       <c r="F126" s="6">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G126" s="6" t="s">
         <v>11</v>
@@ -10736,7 +10736,7 @@
         <v>49</v>
       </c>
       <c r="F127" s="8">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G127" s="8" t="s">
         <v>11</v>
@@ -10759,7 +10759,7 @@
         <v>49</v>
       </c>
       <c r="F128" s="6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G128" s="6" t="s">
         <v>11</v>
@@ -10782,7 +10782,7 @@
         <v>49</v>
       </c>
       <c r="F129" s="8">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G129" s="8" t="s">
         <v>11</v>
@@ -10805,7 +10805,7 @@
         <v>49</v>
       </c>
       <c r="F130" s="6">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
         <v>11</v>
@@ -10828,7 +10828,7 @@
         <v>49</v>
       </c>
       <c r="F131" s="8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G131" s="8" t="s">
         <v>11</v>
@@ -10851,7 +10851,7 @@
         <v>49</v>
       </c>
       <c r="F132" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G132" s="6" t="s">
         <v>11</v>
@@ -10897,7 +10897,7 @@
         <v>49</v>
       </c>
       <c r="F134" s="6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G134" s="6" t="s">
         <v>11</v>
@@ -10920,7 +10920,7 @@
         <v>49</v>
       </c>
       <c r="F135" s="8">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G135" s="8" t="s">
         <v>11</v>
@@ -10943,7 +10943,7 @@
         <v>49</v>
       </c>
       <c r="F136" s="6">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
         <v>11</v>
@@ -11012,7 +11012,7 @@
         <v>49</v>
       </c>
       <c r="F139" s="8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G139" s="8" t="s">
         <v>11</v>
@@ -11035,7 +11035,7 @@
         <v>49</v>
       </c>
       <c r="F140" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G140" s="6" t="s">
         <v>11</v>
@@ -11081,7 +11081,7 @@
         <v>49</v>
       </c>
       <c r="F142" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G142" s="6" t="s">
         <v>11</v>
@@ -11127,7 +11127,7 @@
         <v>49</v>
       </c>
       <c r="F144" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G144" s="6" t="s">
         <v>11</v>
@@ -11150,7 +11150,7 @@
         <v>49</v>
       </c>
       <c r="F145" s="8">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G145" s="8" t="s">
         <v>11</v>
@@ -11173,7 +11173,7 @@
         <v>49</v>
       </c>
       <c r="F146" s="6">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="G146" s="6" t="s">
         <v>11</v>
@@ -11196,7 +11196,7 @@
         <v>49</v>
       </c>
       <c r="F147" s="8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G147" s="8" t="s">
         <v>11</v>
@@ -11219,7 +11219,7 @@
         <v>49</v>
       </c>
       <c r="F148" s="6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G148" s="6" t="s">
         <v>11</v>
@@ -11242,7 +11242,7 @@
         <v>49</v>
       </c>
       <c r="F149" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G149" s="8" t="s">
         <v>11</v>
@@ -11265,7 +11265,7 @@
         <v>49</v>
       </c>
       <c r="F150" s="6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G150" s="6" t="s">
         <v>11</v>
@@ -11288,7 +11288,7 @@
         <v>49</v>
       </c>
       <c r="F151" s="8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G151" s="8" t="s">
         <v>11</v>
@@ -11311,7 +11311,7 @@
         <v>49</v>
       </c>
       <c r="F152" s="6">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G152" s="6" t="s">
         <v>11</v>
@@ -11334,7 +11334,7 @@
         <v>49</v>
       </c>
       <c r="F153" s="8">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G153" s="8" t="s">
         <v>11</v>
@@ -11357,7 +11357,7 @@
         <v>49</v>
       </c>
       <c r="F154" s="6">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="G154" s="6" t="s">
         <v>11</v>
@@ -11380,7 +11380,7 @@
         <v>49</v>
       </c>
       <c r="F155" s="8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G155" s="8" t="s">
         <v>11</v>
@@ -11403,7 +11403,7 @@
         <v>49</v>
       </c>
       <c r="F156" s="6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G156" s="6" t="s">
         <v>11</v>
@@ -11449,7 +11449,7 @@
         <v>49</v>
       </c>
       <c r="F158" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G158" s="6" t="s">
         <v>11</v>
@@ -11472,7 +11472,7 @@
         <v>49</v>
       </c>
       <c r="F159" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G159" s="8" t="s">
         <v>11</v>
@@ -11495,7 +11495,7 @@
         <v>49</v>
       </c>
       <c r="F160" s="6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G160" s="6" t="s">
         <v>11</v>
@@ -11518,7 +11518,7 @@
         <v>49</v>
       </c>
       <c r="F161" s="8">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G161" s="8" t="s">
         <v>11</v>
@@ -11541,7 +11541,7 @@
         <v>49</v>
       </c>
       <c r="F162" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G162" s="6" t="s">
         <v>11</v>
@@ -11564,7 +11564,7 @@
         <v>49</v>
       </c>
       <c r="F163" s="8">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G163" s="8" t="s">
         <v>11</v>
@@ -11587,7 +11587,7 @@
         <v>49</v>
       </c>
       <c r="F164" s="6">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="G164" s="6" t="s">
         <v>11</v>
@@ -11633,7 +11633,7 @@
         <v>49</v>
       </c>
       <c r="F166" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G166" s="6" t="s">
         <v>11</v>
@@ -11656,7 +11656,7 @@
         <v>49</v>
       </c>
       <c r="F167" s="8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G167" s="8" t="s">
         <v>11</v>
@@ -11679,7 +11679,7 @@
         <v>49</v>
       </c>
       <c r="F168" s="6">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G168" s="6" t="s">
         <v>11</v>
@@ -11702,7 +11702,7 @@
         <v>49</v>
       </c>
       <c r="F169" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G169" s="8" t="s">
         <v>11</v>
@@ -11748,7 +11748,7 @@
         <v>49</v>
       </c>
       <c r="F171" s="8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G171" s="8" t="s">
         <v>11</v>
@@ -11771,7 +11771,7 @@
         <v>49</v>
       </c>
       <c r="F172" s="6">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G172" s="6" t="s">
         <v>11</v>
@@ -11794,7 +11794,7 @@
         <v>49</v>
       </c>
       <c r="F173" s="8">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G173" s="8" t="s">
         <v>11</v>
@@ -11817,7 +11817,7 @@
         <v>49</v>
       </c>
       <c r="F174" s="6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G174" s="6" t="s">
         <v>11</v>
@@ -11840,7 +11840,7 @@
         <v>49</v>
       </c>
       <c r="F175" s="8">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G175" s="8" t="s">
         <v>11</v>
@@ -11863,7 +11863,7 @@
         <v>49</v>
       </c>
       <c r="F176" s="6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G176" s="6" t="s">
         <v>11</v>
@@ -11886,7 +11886,7 @@
         <v>49</v>
       </c>
       <c r="F177" s="8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G177" s="8" t="s">
         <v>11</v>
@@ -11909,7 +11909,7 @@
         <v>49</v>
       </c>
       <c r="F178" s="6">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G178" s="6" t="s">
         <v>11</v>
@@ -11955,7 +11955,7 @@
         <v>49</v>
       </c>
       <c r="F180" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G180" s="6" t="s">
         <v>11</v>
@@ -12024,7 +12024,7 @@
         <v>49</v>
       </c>
       <c r="F183" s="8">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G183" s="8" t="s">
         <v>11</v>
@@ -12047,7 +12047,7 @@
         <v>49</v>
       </c>
       <c r="F184" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G184" s="6" t="s">
         <v>11</v>
@@ -12070,7 +12070,7 @@
         <v>49</v>
       </c>
       <c r="F185" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G185" s="8" t="s">
         <v>11</v>
@@ -12093,7 +12093,7 @@
         <v>49</v>
       </c>
       <c r="F186" s="6">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G186" s="6" t="s">
         <v>11</v>
@@ -12116,7 +12116,7 @@
         <v>49</v>
       </c>
       <c r="F187" s="8">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G187" s="8" t="s">
         <v>11</v>
@@ -12139,7 +12139,7 @@
         <v>49</v>
       </c>
       <c r="F188" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G188" s="6" t="s">
         <v>11</v>
@@ -12162,7 +12162,7 @@
         <v>49</v>
       </c>
       <c r="F189" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G189" s="8" t="s">
         <v>11</v>
@@ -12185,7 +12185,7 @@
         <v>49</v>
       </c>
       <c r="F190" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G190" s="6" t="s">
         <v>11</v>
@@ -12208,7 +12208,7 @@
         <v>49</v>
       </c>
       <c r="F191" s="8">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G191" s="8" t="s">
         <v>11</v>
@@ -12254,7 +12254,7 @@
         <v>49</v>
       </c>
       <c r="F193" s="8">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G193" s="8" t="s">
         <v>11</v>
@@ -12277,7 +12277,7 @@
         <v>49</v>
       </c>
       <c r="F194" s="6">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G194" s="6" t="s">
         <v>11</v>
@@ -12300,7 +12300,7 @@
         <v>49</v>
       </c>
       <c r="F195" s="8">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G195" s="8" t="s">
         <v>11</v>
@@ -12346,7 +12346,7 @@
         <v>49</v>
       </c>
       <c r="F197" s="8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G197" s="8" t="s">
         <v>11</v>
@@ -12369,7 +12369,7 @@
         <v>49</v>
       </c>
       <c r="F198" s="6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G198" s="6" t="s">
         <v>11</v>
@@ -12415,7 +12415,7 @@
         <v>49</v>
       </c>
       <c r="F200" s="6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G200" s="6" t="s">
         <v>11</v>
@@ -12438,7 +12438,7 @@
         <v>49</v>
       </c>
       <c r="F201" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G201" s="8" t="s">
         <v>11</v>
@@ -12461,7 +12461,7 @@
         <v>49</v>
       </c>
       <c r="F202" s="6">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G202" s="6" t="s">
         <v>11</v>
@@ -12484,7 +12484,7 @@
         <v>49</v>
       </c>
       <c r="F203" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G203" s="8" t="s">
         <v>11</v>
@@ -12507,7 +12507,7 @@
         <v>49</v>
       </c>
       <c r="F204" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G204" s="6" t="s">
         <v>11</v>
@@ -12530,7 +12530,7 @@
         <v>49</v>
       </c>
       <c r="F205" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G205" s="8" t="s">
         <v>11</v>
@@ -12553,7 +12553,7 @@
         <v>49</v>
       </c>
       <c r="F206" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G206" s="6" t="s">
         <v>11</v>
@@ -12576,7 +12576,7 @@
         <v>49</v>
       </c>
       <c r="F207" s="8">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G207" s="8" t="s">
         <v>11</v>
@@ -12599,7 +12599,7 @@
         <v>49</v>
       </c>
       <c r="F208" s="6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G208" s="6" t="s">
         <v>11</v>
@@ -12622,7 +12622,7 @@
         <v>49</v>
       </c>
       <c r="F209" s="8">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G209" s="8" t="s">
         <v>11</v>
@@ -12645,7 +12645,7 @@
         <v>49</v>
       </c>
       <c r="F210" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G210" s="6" t="s">
         <v>11</v>
@@ -12668,7 +12668,7 @@
         <v>49</v>
       </c>
       <c r="F211" s="8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G211" s="8" t="s">
         <v>11</v>
@@ -12691,7 +12691,7 @@
         <v>49</v>
       </c>
       <c r="F212" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G212" s="6" t="s">
         <v>11</v>
@@ -12737,7 +12737,7 @@
         <v>49</v>
       </c>
       <c r="F214" s="6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G214" s="6" t="s">
         <v>11</v>
@@ -12760,7 +12760,7 @@
         <v>49</v>
       </c>
       <c r="F215" s="8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G215" s="8" t="s">
         <v>11</v>
@@ -12783,7 +12783,7 @@
         <v>49</v>
       </c>
       <c r="F216" s="6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G216" s="6" t="s">
         <v>11</v>
@@ -12806,7 +12806,7 @@
         <v>49</v>
       </c>
       <c r="F217" s="8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G217" s="8" t="s">
         <v>11</v>
@@ -12829,7 +12829,7 @@
         <v>49</v>
       </c>
       <c r="F218" s="6">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G218" s="6" t="s">
         <v>11</v>
@@ -12852,7 +12852,7 @@
         <v>49</v>
       </c>
       <c r="F219" s="8">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="G219" s="8" t="s">
         <v>11</v>
@@ -12875,7 +12875,7 @@
         <v>49</v>
       </c>
       <c r="F220" s="6">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G220" s="6" t="s">
         <v>11</v>
@@ -12898,7 +12898,7 @@
         <v>49</v>
       </c>
       <c r="F221" s="8">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G221" s="8" t="s">
         <v>11</v>
@@ -12921,7 +12921,7 @@
         <v>49</v>
       </c>
       <c r="F222" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G222" s="6" t="s">
         <v>11</v>
@@ -12944,7 +12944,7 @@
         <v>49</v>
       </c>
       <c r="F223" s="8">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G223" s="8" t="s">
         <v>11</v>
@@ -12967,7 +12967,7 @@
         <v>49</v>
       </c>
       <c r="F224" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G224" s="6" t="s">
         <v>11</v>
@@ -12990,7 +12990,7 @@
         <v>49</v>
       </c>
       <c r="F225" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G225" s="8" t="s">
         <v>11</v>
@@ -13013,7 +13013,7 @@
         <v>49</v>
       </c>
       <c r="F226" s="6">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G226" s="6" t="s">
         <v>11</v>
@@ -13036,7 +13036,7 @@
         <v>49</v>
       </c>
       <c r="F227" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G227" s="8" t="s">
         <v>11</v>
@@ -13059,7 +13059,7 @@
         <v>49</v>
       </c>
       <c r="F228" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G228" s="6" t="s">
         <v>11</v>
@@ -13082,7 +13082,7 @@
         <v>49</v>
       </c>
       <c r="F229" s="8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G229" s="8" t="s">
         <v>11</v>
@@ -13105,7 +13105,7 @@
         <v>49</v>
       </c>
       <c r="F230" s="6">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G230" s="6" t="s">
         <v>11</v>
@@ -13128,7 +13128,7 @@
         <v>49</v>
       </c>
       <c r="F231" s="8">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G231" s="8" t="s">
         <v>11</v>
@@ -13151,7 +13151,7 @@
         <v>49</v>
       </c>
       <c r="F232" s="6">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G232" s="6" t="s">
         <v>11</v>
@@ -13197,7 +13197,7 @@
         <v>49</v>
       </c>
       <c r="F234" s="6">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G234" s="6" t="s">
         <v>11</v>
@@ -13243,7 +13243,7 @@
         <v>49</v>
       </c>
       <c r="F236" s="6">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G236" s="6" t="s">
         <v>11</v>
@@ -13266,7 +13266,7 @@
         <v>49</v>
       </c>
       <c r="F237" s="8">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G237" s="8" t="s">
         <v>11</v>
@@ -13289,7 +13289,7 @@
         <v>49</v>
       </c>
       <c r="F238" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G238" s="6" t="s">
         <v>11</v>
@@ -13312,7 +13312,7 @@
         <v>49</v>
       </c>
       <c r="F239" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G239" s="8" t="s">
         <v>11</v>
@@ -13381,7 +13381,7 @@
         <v>49</v>
       </c>
       <c r="F242" s="6">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G242" s="6" t="s">
         <v>11</v>
@@ -13404,7 +13404,7 @@
         <v>49</v>
       </c>
       <c r="F243" s="8">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G243" s="8" t="s">
         <v>11</v>
@@ -13427,7 +13427,7 @@
         <v>49</v>
       </c>
       <c r="F244" s="6">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G244" s="6" t="s">
         <v>11</v>
@@ -13473,7 +13473,7 @@
         <v>49</v>
       </c>
       <c r="F246" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G246" s="6" t="s">
         <v>11</v>
@@ -13496,7 +13496,7 @@
         <v>49</v>
       </c>
       <c r="F247" s="8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G247" s="8" t="s">
         <v>11</v>
@@ -13519,7 +13519,7 @@
         <v>49</v>
       </c>
       <c r="F248" s="6">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="G248" s="6" t="s">
         <v>11</v>
@@ -13542,7 +13542,7 @@
         <v>49</v>
       </c>
       <c r="F249" s="8">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G249" s="8" t="s">
         <v>11</v>
@@ -13565,7 +13565,7 @@
         <v>49</v>
       </c>
       <c r="F250" s="6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G250" s="6" t="s">
         <v>11</v>
@@ -13588,7 +13588,7 @@
         <v>49</v>
       </c>
       <c r="F251" s="8">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G251" s="8" t="s">
         <v>11</v>
@@ -13611,7 +13611,7 @@
         <v>49</v>
       </c>
       <c r="F252" s="6">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="G252" s="6" t="s">
         <v>11</v>
@@ -13657,7 +13657,7 @@
         <v>49</v>
       </c>
       <c r="F254" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G254" s="6" t="s">
         <v>11</v>
@@ -13680,7 +13680,7 @@
         <v>49</v>
       </c>
       <c r="F255" s="8">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G255" s="8" t="s">
         <v>11</v>
@@ -13703,7 +13703,7 @@
         <v>49</v>
       </c>
       <c r="F256" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G256" s="6" t="s">
         <v>11</v>
@@ -13726,7 +13726,7 @@
         <v>49</v>
       </c>
       <c r="F257" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G257" s="8" t="s">
         <v>11</v>
@@ -13749,7 +13749,7 @@
         <v>49</v>
       </c>
       <c r="F258" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G258" s="6" t="s">
         <v>11</v>
@@ -13772,7 +13772,7 @@
         <v>49</v>
       </c>
       <c r="F259" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G259" s="8" t="s">
         <v>11</v>
@@ -13795,7 +13795,7 @@
         <v>49</v>
       </c>
       <c r="F260" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G260" s="6" t="s">
         <v>11</v>
@@ -13818,7 +13818,7 @@
         <v>49</v>
       </c>
       <c r="F261" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G261" s="8" t="s">
         <v>11</v>
@@ -13841,7 +13841,7 @@
         <v>49</v>
       </c>
       <c r="F262" s="6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G262" s="6" t="s">
         <v>11</v>
@@ -13864,7 +13864,7 @@
         <v>49</v>
       </c>
       <c r="F263" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G263" s="8" t="s">
         <v>11</v>
@@ -13910,7 +13910,7 @@
         <v>49</v>
       </c>
       <c r="F265" s="8">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G265" s="8" t="s">
         <v>11</v>
@@ -13933,7 +13933,7 @@
         <v>49</v>
       </c>
       <c r="F266" s="6">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G266" s="6" t="s">
         <v>11</v>
@@ -13979,7 +13979,7 @@
         <v>49</v>
       </c>
       <c r="F268" s="6">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G268" s="6" t="s">
         <v>11</v>
@@ -14002,7 +14002,7 @@
         <v>49</v>
       </c>
       <c r="F269" s="8">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G269" s="8" t="s">
         <v>11</v>
@@ -14025,7 +14025,7 @@
         <v>49</v>
       </c>
       <c r="F270" s="6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G270" s="6" t="s">
         <v>11</v>
@@ -14048,7 +14048,7 @@
         <v>49</v>
       </c>
       <c r="F271" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G271" s="8" t="s">
         <v>11</v>
@@ -14071,7 +14071,7 @@
         <v>49</v>
       </c>
       <c r="F272" s="6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G272" s="6" t="s">
         <v>11</v>
@@ -14094,7 +14094,7 @@
         <v>49</v>
       </c>
       <c r="F273" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G273" s="8" t="s">
         <v>11</v>
@@ -14140,7 +14140,7 @@
         <v>49</v>
       </c>
       <c r="F275" s="8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G275" s="8" t="s">
         <v>11</v>
@@ -14163,7 +14163,7 @@
         <v>49</v>
       </c>
       <c r="F276" s="6">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G276" s="6" t="s">
         <v>11</v>
@@ -14209,7 +14209,7 @@
         <v>49</v>
       </c>
       <c r="F278" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G278" s="6" t="s">
         <v>11</v>
@@ -14255,7 +14255,7 @@
         <v>49</v>
       </c>
       <c r="F280" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G280" s="6" t="s">
         <v>11</v>
@@ -14278,7 +14278,7 @@
         <v>49</v>
       </c>
       <c r="F281" s="8">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G281" s="8" t="s">
         <v>11</v>
@@ -14301,7 +14301,7 @@
         <v>49</v>
       </c>
       <c r="F282" s="6">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G282" s="6" t="s">
         <v>11</v>
@@ -14324,7 +14324,7 @@
         <v>49</v>
       </c>
       <c r="F283" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G283" s="8" t="s">
         <v>11</v>
@@ -14370,7 +14370,7 @@
         <v>49</v>
       </c>
       <c r="F285" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G285" s="8" t="s">
         <v>11</v>
@@ -14393,7 +14393,7 @@
         <v>49</v>
       </c>
       <c r="F286" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G286" s="6" t="s">
         <v>11</v>
@@ -14416,7 +14416,7 @@
         <v>49</v>
       </c>
       <c r="F287" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G287" s="8" t="s">
         <v>11</v>
@@ -14439,7 +14439,7 @@
         <v>49</v>
       </c>
       <c r="F288" s="6">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="G288" s="6" t="s">
         <v>11</v>
@@ -14462,7 +14462,7 @@
         <v>49</v>
       </c>
       <c r="F289" s="8">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G289" s="8" t="s">
         <v>11</v>
@@ -14485,7 +14485,7 @@
         <v>49</v>
       </c>
       <c r="F290" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G290" s="6" t="s">
         <v>11</v>
@@ -14508,7 +14508,7 @@
         <v>49</v>
       </c>
       <c r="F291" s="8">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="G291" s="8" t="s">
         <v>11</v>
@@ -14531,7 +14531,7 @@
         <v>49</v>
       </c>
       <c r="F292" s="6">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G292" s="6" t="s">
         <v>11</v>
@@ -14554,7 +14554,7 @@
         <v>49</v>
       </c>
       <c r="F293" s="8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G293" s="8" t="s">
         <v>11</v>
@@ -14577,7 +14577,7 @@
         <v>49</v>
       </c>
       <c r="F294" s="6">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G294" s="6" t="s">
         <v>11</v>
@@ -14600,7 +14600,7 @@
         <v>49</v>
       </c>
       <c r="F295" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G295" s="8" t="s">
         <v>11</v>
@@ -14623,7 +14623,7 @@
         <v>49</v>
       </c>
       <c r="F296" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G296" s="6" t="s">
         <v>11</v>
@@ -14669,7 +14669,7 @@
         <v>49</v>
       </c>
       <c r="F298" s="6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G298" s="6" t="s">
         <v>11</v>
@@ -14692,7 +14692,7 @@
         <v>49</v>
       </c>
       <c r="F299" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G299" s="8" t="s">
         <v>11</v>
@@ -14715,7 +14715,7 @@
         <v>49</v>
       </c>
       <c r="F300" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G300" s="6" t="s">
         <v>11</v>
@@ -14738,7 +14738,7 @@
         <v>49</v>
       </c>
       <c r="F301" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G301" s="8" t="s">
         <v>11</v>
@@ -14784,7 +14784,7 @@
         <v>49</v>
       </c>
       <c r="F303" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G303" s="8" t="s">
         <v>11</v>
@@ -14807,7 +14807,7 @@
         <v>49</v>
       </c>
       <c r="F304" s="6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G304" s="6" t="s">
         <v>11</v>
@@ -14830,7 +14830,7 @@
         <v>49</v>
       </c>
       <c r="F305" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G305" s="8" t="s">
         <v>11</v>
@@ -14853,7 +14853,7 @@
         <v>49</v>
       </c>
       <c r="F306" s="6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G306" s="6" t="s">
         <v>11</v>
@@ -14876,7 +14876,7 @@
         <v>49</v>
       </c>
       <c r="F307" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G307" s="8" t="s">
         <v>11</v>
@@ -14899,7 +14899,7 @@
         <v>49</v>
       </c>
       <c r="F308" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G308" s="6" t="s">
         <v>11</v>
@@ -14922,7 +14922,7 @@
         <v>49</v>
       </c>
       <c r="F309" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G309" s="8" t="s">
         <v>11</v>
@@ -14945,7 +14945,7 @@
         <v>49</v>
       </c>
       <c r="F310" s="6">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="G310" s="6" t="s">
         <v>11</v>
@@ -14968,7 +14968,7 @@
         <v>49</v>
       </c>
       <c r="F311" s="8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G311" s="8" t="s">
         <v>11</v>
@@ -14991,7 +14991,7 @@
         <v>49</v>
       </c>
       <c r="F312" s="6">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G312" s="6" t="s">
         <v>11</v>
@@ -15014,7 +15014,7 @@
         <v>49</v>
       </c>
       <c r="F313" s="8">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G313" s="8" t="s">
         <v>11</v>
@@ -15037,7 +15037,7 @@
         <v>49</v>
       </c>
       <c r="F314" s="6">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G314" s="6" t="s">
         <v>11</v>
@@ -15060,7 +15060,7 @@
         <v>49</v>
       </c>
       <c r="F315" s="8">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G315" s="8" t="s">
         <v>11</v>
@@ -15083,7 +15083,7 @@
         <v>49</v>
       </c>
       <c r="F316" s="6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G316" s="6" t="s">
         <v>11</v>
@@ -15106,7 +15106,7 @@
         <v>49</v>
       </c>
       <c r="F317" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G317" s="8" t="s">
         <v>11</v>
@@ -15129,7 +15129,7 @@
         <v>49</v>
       </c>
       <c r="F318" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G318" s="6" t="s">
         <v>11</v>
@@ -15152,7 +15152,7 @@
         <v>49</v>
       </c>
       <c r="F319" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G319" s="8" t="s">
         <v>11</v>
@@ -15198,7 +15198,7 @@
         <v>49</v>
       </c>
       <c r="F321" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G321" s="8" t="s">
         <v>11</v>
@@ -15221,7 +15221,7 @@
         <v>49</v>
       </c>
       <c r="F322" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G322" s="6" t="s">
         <v>11</v>
@@ -15244,7 +15244,7 @@
         <v>49</v>
       </c>
       <c r="F323" s="8">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G323" s="8" t="s">
         <v>11</v>
@@ -15267,7 +15267,7 @@
         <v>49</v>
       </c>
       <c r="F324" s="6">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G324" s="6" t="s">
         <v>11</v>
@@ -15290,7 +15290,7 @@
         <v>49</v>
       </c>
       <c r="F325" s="8">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G325" s="8" t="s">
         <v>11</v>
@@ -15313,7 +15313,7 @@
         <v>49</v>
       </c>
       <c r="F326" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G326" s="6" t="s">
         <v>11</v>
@@ -15336,7 +15336,7 @@
         <v>49</v>
       </c>
       <c r="F327" s="8">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G327" s="8" t="s">
         <v>11</v>
@@ -15359,7 +15359,7 @@
         <v>49</v>
       </c>
       <c r="F328" s="6">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G328" s="6" t="s">
         <v>11</v>
@@ -15382,7 +15382,7 @@
         <v>49</v>
       </c>
       <c r="F329" s="8">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G329" s="8" t="s">
         <v>11</v>
@@ -15405,7 +15405,7 @@
         <v>49</v>
       </c>
       <c r="F330" s="6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G330" s="6" t="s">
         <v>11</v>
@@ -15428,7 +15428,7 @@
         <v>49</v>
       </c>
       <c r="F331" s="8">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G331" s="8" t="s">
         <v>11</v>
@@ -15451,7 +15451,7 @@
         <v>49</v>
       </c>
       <c r="F332" s="6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G332" s="6" t="s">
         <v>11</v>
@@ -15497,7 +15497,7 @@
         <v>49</v>
       </c>
       <c r="F334" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G334" s="6" t="s">
         <v>11</v>
@@ -15543,7 +15543,7 @@
         <v>49</v>
       </c>
       <c r="F336" s="6">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G336" s="6" t="s">
         <v>11</v>
@@ -15566,7 +15566,7 @@
         <v>49</v>
       </c>
       <c r="F337" s="8">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G337" s="8" t="s">
         <v>11</v>
@@ -15589,7 +15589,7 @@
         <v>49</v>
       </c>
       <c r="F338" s="6">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G338" s="6" t="s">
         <v>11</v>
@@ -15635,7 +15635,7 @@
         <v>49</v>
       </c>
       <c r="F340" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G340" s="6" t="s">
         <v>11</v>
@@ -15658,7 +15658,7 @@
         <v>49</v>
       </c>
       <c r="F341" s="8">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G341" s="8" t="s">
         <v>11</v>
@@ -15681,7 +15681,7 @@
         <v>49</v>
       </c>
       <c r="F342" s="6">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G342" s="6" t="s">
         <v>11</v>
@@ -15704,7 +15704,7 @@
         <v>49</v>
       </c>
       <c r="F343" s="8">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G343" s="8" t="s">
         <v>11</v>
@@ -15727,7 +15727,7 @@
         <v>49</v>
       </c>
       <c r="F344" s="6">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G344" s="6" t="s">
         <v>11</v>
@@ -15750,7 +15750,7 @@
         <v>49</v>
       </c>
       <c r="F345" s="8">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G345" s="8" t="s">
         <v>11</v>
@@ -15773,7 +15773,7 @@
         <v>49</v>
       </c>
       <c r="F346" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G346" s="6" t="s">
         <v>11</v>
@@ -15796,7 +15796,7 @@
         <v>49</v>
       </c>
       <c r="F347" s="8">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G347" s="8" t="s">
         <v>11</v>
@@ -15819,7 +15819,7 @@
         <v>49</v>
       </c>
       <c r="F348" s="6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G348" s="6" t="s">
         <v>11</v>
@@ -15842,7 +15842,7 @@
         <v>49</v>
       </c>
       <c r="F349" s="8">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="G349" s="8" t="s">
         <v>11</v>
@@ -15865,7 +15865,7 @@
         <v>49</v>
       </c>
       <c r="F350" s="6">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G350" s="6" t="s">
         <v>11</v>
@@ -15888,7 +15888,7 @@
         <v>49</v>
       </c>
       <c r="F351" s="8">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G351" s="8" t="s">
         <v>11</v>
@@ -15911,7 +15911,7 @@
         <v>49</v>
       </c>
       <c r="F352" s="6">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G352" s="6" t="s">
         <v>11</v>
@@ -15934,7 +15934,7 @@
         <v>49</v>
       </c>
       <c r="F353" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G353" s="8" t="s">
         <v>11</v>
@@ -15957,7 +15957,7 @@
         <v>49</v>
       </c>
       <c r="F354" s="6">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G354" s="6" t="s">
         <v>11</v>
@@ -15980,7 +15980,7 @@
         <v>49</v>
       </c>
       <c r="F355" s="8">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G355" s="8" t="s">
         <v>11</v>
@@ -16026,7 +16026,7 @@
         <v>49</v>
       </c>
       <c r="F357" s="8">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G357" s="8" t="s">
         <v>11</v>
@@ -16049,7 +16049,7 @@
         <v>49</v>
       </c>
       <c r="F358" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G358" s="6" t="s">
         <v>11</v>
@@ -16072,7 +16072,7 @@
         <v>49</v>
       </c>
       <c r="F359" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G359" s="8" t="s">
         <v>11</v>
@@ -16095,7 +16095,7 @@
         <v>49</v>
       </c>
       <c r="F360" s="6">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G360" s="6" t="s">
         <v>11</v>
@@ -16118,7 +16118,7 @@
         <v>49</v>
       </c>
       <c r="F361" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G361" s="8" t="s">
         <v>11</v>
@@ -16141,7 +16141,7 @@
         <v>49</v>
       </c>
       <c r="F362" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G362" s="6" t="s">
         <v>11</v>
@@ -16164,7 +16164,7 @@
         <v>49</v>
       </c>
       <c r="F363" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G363" s="8" t="s">
         <v>11</v>
@@ -16187,7 +16187,7 @@
         <v>49</v>
       </c>
       <c r="F364" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G364" s="6" t="s">
         <v>11</v>
@@ -16210,7 +16210,7 @@
         <v>49</v>
       </c>
       <c r="F365" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G365" s="8" t="s">
         <v>11</v>
@@ -16233,7 +16233,7 @@
         <v>49</v>
       </c>
       <c r="F366" s="6">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G366" s="6" t="s">
         <v>11</v>
@@ -16256,7 +16256,7 @@
         <v>49</v>
       </c>
       <c r="F367" s="8">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="G367" s="8" t="s">
         <v>11</v>
@@ -16279,7 +16279,7 @@
         <v>49</v>
       </c>
       <c r="F368" s="6">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G368" s="6" t="s">
         <v>11</v>
@@ -16325,7 +16325,7 @@
         <v>49</v>
       </c>
       <c r="F370" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G370" s="6" t="s">
         <v>11</v>
@@ -16348,7 +16348,7 @@
         <v>49</v>
       </c>
       <c r="F371" s="8">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G371" s="8" t="s">
         <v>11</v>
@@ -16394,7 +16394,7 @@
         <v>49</v>
       </c>
       <c r="F373" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G373" s="8" t="s">
         <v>11</v>
@@ -16417,7 +16417,7 @@
         <v>49</v>
       </c>
       <c r="F374" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G374" s="6" t="s">
         <v>11</v>
@@ -16440,7 +16440,7 @@
         <v>49</v>
       </c>
       <c r="F375" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G375" s="8" t="s">
         <v>11</v>
@@ -16463,7 +16463,7 @@
         <v>49</v>
       </c>
       <c r="F376" s="6">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="G376" s="6" t="s">
         <v>11</v>
@@ -16486,7 +16486,7 @@
         <v>49</v>
       </c>
       <c r="F377" s="8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G377" s="8" t="s">
         <v>11</v>
@@ -16509,7 +16509,7 @@
         <v>49</v>
       </c>
       <c r="F378" s="6">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G378" s="6" t="s">
         <v>11</v>
@@ -16555,7 +16555,7 @@
         <v>49</v>
       </c>
       <c r="F380" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G380" s="6" t="s">
         <v>11</v>
@@ -16578,7 +16578,7 @@
         <v>49</v>
       </c>
       <c r="F381" s="8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G381" s="8" t="s">
         <v>11</v>
@@ -16624,7 +16624,7 @@
         <v>49</v>
       </c>
       <c r="F383" s="8">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G383" s="8" t="s">
         <v>11</v>
@@ -16647,7 +16647,7 @@
         <v>49</v>
       </c>
       <c r="F384" s="6">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G384" s="6" t="s">
         <v>11</v>
@@ -16670,7 +16670,7 @@
         <v>49</v>
       </c>
       <c r="F385" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G385" s="8" t="s">
         <v>11</v>
@@ -16693,7 +16693,7 @@
         <v>49</v>
       </c>
       <c r="F386" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G386" s="6" t="s">
         <v>11</v>
@@ -16739,7 +16739,7 @@
         <v>49</v>
       </c>
       <c r="F388" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G388" s="6" t="s">
         <v>11</v>
@@ -16762,7 +16762,7 @@
         <v>49</v>
       </c>
       <c r="F389" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G389" s="8" t="s">
         <v>11</v>
@@ -16785,7 +16785,7 @@
         <v>49</v>
       </c>
       <c r="F390" s="6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G390" s="6" t="s">
         <v>11</v>
@@ -16808,7 +16808,7 @@
         <v>49</v>
       </c>
       <c r="F391" s="8">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="G391" s="8" t="s">
         <v>11</v>
@@ -16831,7 +16831,7 @@
         <v>49</v>
       </c>
       <c r="F392" s="6">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G392" s="6" t="s">
         <v>11</v>
@@ -16854,7 +16854,7 @@
         <v>49</v>
       </c>
       <c r="F393" s="8">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G393" s="8" t="s">
         <v>11</v>
@@ -16877,7 +16877,7 @@
         <v>49</v>
       </c>
       <c r="F394" s="6">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G394" s="6" t="s">
         <v>11</v>
@@ -16900,7 +16900,7 @@
         <v>49</v>
       </c>
       <c r="F395" s="8">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G395" s="8" t="s">
         <v>11</v>
@@ -16923,7 +16923,7 @@
         <v>49</v>
       </c>
       <c r="F396" s="6">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G396" s="6" t="s">
         <v>11</v>
@@ -16946,7 +16946,7 @@
         <v>49</v>
       </c>
       <c r="F397" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G397" s="8" t="s">
         <v>11</v>
@@ -16969,7 +16969,7 @@
         <v>49</v>
       </c>
       <c r="F398" s="6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G398" s="6" t="s">
         <v>11</v>
@@ -16992,7 +16992,7 @@
         <v>49</v>
       </c>
       <c r="F399" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G399" s="8" t="s">
         <v>11</v>
@@ -17015,7 +17015,7 @@
         <v>49</v>
       </c>
       <c r="F400" s="6">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G400" s="6" t="s">
         <v>11</v>
@@ -17038,7 +17038,7 @@
         <v>49</v>
       </c>
       <c r="F401" s="8">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G401" s="8" t="s">
         <v>11</v>
@@ -17061,7 +17061,7 @@
         <v>49</v>
       </c>
       <c r="F402" s="6">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G402" s="6" t="s">
         <v>11</v>
@@ -17107,7 +17107,7 @@
         <v>49</v>
       </c>
       <c r="F404" s="6">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G404" s="6" t="s">
         <v>11</v>
@@ -17130,7 +17130,7 @@
         <v>49</v>
       </c>
       <c r="F405" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G405" s="8" t="s">
         <v>11</v>
@@ -17176,7 +17176,7 @@
         <v>49</v>
       </c>
       <c r="F407" s="8">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="G407" s="8" t="s">
         <v>11</v>
@@ -17199,7 +17199,7 @@
         <v>49</v>
       </c>
       <c r="F408" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G408" s="6" t="s">
         <v>11</v>
@@ -17222,7 +17222,7 @@
         <v>49</v>
       </c>
       <c r="F409" s="8">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G409" s="8" t="s">
         <v>11</v>
@@ -17245,7 +17245,7 @@
         <v>49</v>
       </c>
       <c r="F410" s="6">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="G410" s="6" t="s">
         <v>11</v>
@@ -17314,7 +17314,7 @@
         <v>49</v>
       </c>
       <c r="F413" s="8">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G413" s="8" t="s">
         <v>11</v>
@@ -17337,7 +17337,7 @@
         <v>49</v>
       </c>
       <c r="F414" s="6">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G414" s="6" t="s">
         <v>11</v>
@@ -17360,7 +17360,7 @@
         <v>49</v>
       </c>
       <c r="F415" s="8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G415" s="8" t="s">
         <v>11</v>
@@ -17406,7 +17406,7 @@
         <v>49</v>
       </c>
       <c r="F417" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G417" s="8" t="s">
         <v>11</v>
@@ -17429,7 +17429,7 @@
         <v>49</v>
       </c>
       <c r="F418" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G418" s="6" t="s">
         <v>11</v>
@@ -17452,7 +17452,7 @@
         <v>49</v>
       </c>
       <c r="F419" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G419" s="8" t="s">
         <v>11</v>
@@ -17475,7 +17475,7 @@
         <v>49</v>
       </c>
       <c r="F420" s="6">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G420" s="6" t="s">
         <v>11</v>
@@ -17498,7 +17498,7 @@
         <v>49</v>
       </c>
       <c r="F421" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G421" s="8" t="s">
         <v>11</v>
@@ -17521,7 +17521,7 @@
         <v>49</v>
       </c>
       <c r="F422" s="6">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G422" s="6" t="s">
         <v>11</v>
@@ -17544,7 +17544,7 @@
         <v>49</v>
       </c>
       <c r="F423" s="8">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G423" s="8" t="s">
         <v>11</v>
@@ -17567,7 +17567,7 @@
         <v>49</v>
       </c>
       <c r="F424" s="6">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G424" s="6" t="s">
         <v>11</v>
@@ -17590,7 +17590,7 @@
         <v>49</v>
       </c>
       <c r="F425" s="8">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G425" s="8" t="s">
         <v>11</v>
@@ -17613,7 +17613,7 @@
         <v>49</v>
       </c>
       <c r="F426" s="6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G426" s="6" t="s">
         <v>11</v>
@@ -17636,7 +17636,7 @@
         <v>49</v>
       </c>
       <c r="F427" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G427" s="8" t="s">
         <v>11</v>
@@ -17659,7 +17659,7 @@
         <v>49</v>
       </c>
       <c r="F428" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G428" s="6" t="s">
         <v>11</v>
@@ -17682,7 +17682,7 @@
         <v>49</v>
       </c>
       <c r="F429" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G429" s="8" t="s">
         <v>11</v>
@@ -17705,7 +17705,7 @@
         <v>49</v>
       </c>
       <c r="F430" s="6">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G430" s="6" t="s">
         <v>11</v>
@@ -17728,7 +17728,7 @@
         <v>49</v>
       </c>
       <c r="F431" s="8">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G431" s="8" t="s">
         <v>11</v>
@@ -17751,7 +17751,7 @@
         <v>49</v>
       </c>
       <c r="F432" s="6">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G432" s="6" t="s">
         <v>11</v>
@@ -17774,7 +17774,7 @@
         <v>49</v>
       </c>
       <c r="F433" s="8">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G433" s="8" t="s">
         <v>11</v>
@@ -17797,7 +17797,7 @@
         <v>49</v>
       </c>
       <c r="F434" s="6">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G434" s="6" t="s">
         <v>11</v>
@@ -17820,7 +17820,7 @@
         <v>49</v>
       </c>
       <c r="F435" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G435" s="8" t="s">
         <v>11</v>
@@ -17843,7 +17843,7 @@
         <v>49</v>
       </c>
       <c r="F436" s="6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G436" s="6" t="s">
         <v>11</v>
@@ -17866,7 +17866,7 @@
         <v>49</v>
       </c>
       <c r="F437" s="8">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G437" s="8" t="s">
         <v>11</v>
@@ -17889,7 +17889,7 @@
         <v>49</v>
       </c>
       <c r="F438" s="6">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G438" s="6" t="s">
         <v>11</v>
@@ -17912,7 +17912,7 @@
         <v>49</v>
       </c>
       <c r="F439" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G439" s="8" t="s">
         <v>11</v>
@@ -17958,7 +17958,7 @@
         <v>49</v>
       </c>
       <c r="F441" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G441" s="8" t="s">
         <v>11</v>
@@ -17981,7 +17981,7 @@
         <v>49</v>
       </c>
       <c r="F442" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G442" s="6" t="s">
         <v>11</v>
@@ -18004,7 +18004,7 @@
         <v>49</v>
       </c>
       <c r="F443" s="8">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G443" s="8" t="s">
         <v>11</v>
@@ -18027,7 +18027,7 @@
         <v>49</v>
       </c>
       <c r="F444" s="6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G444" s="6" t="s">
         <v>11</v>
@@ -18050,7 +18050,7 @@
         <v>49</v>
       </c>
       <c r="F445" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G445" s="8" t="s">
         <v>11</v>
@@ -18073,7 +18073,7 @@
         <v>49</v>
       </c>
       <c r="F446" s="6">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G446" s="6" t="s">
         <v>11</v>
@@ -18096,7 +18096,7 @@
         <v>49</v>
       </c>
       <c r="F447" s="8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G447" s="8" t="s">
         <v>11</v>
@@ -18119,7 +18119,7 @@
         <v>49</v>
       </c>
       <c r="F448" s="6">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G448" s="6" t="s">
         <v>11</v>
@@ -18142,7 +18142,7 @@
         <v>49</v>
       </c>
       <c r="F449" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G449" s="8" t="s">
         <v>11</v>
@@ -18188,7 +18188,7 @@
         <v>49</v>
       </c>
       <c r="F451" s="8">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G451" s="8" t="s">
         <v>11</v>
@@ -18234,7 +18234,7 @@
         <v>49</v>
       </c>
       <c r="F453" s="8">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G453" s="8" t="s">
         <v>11</v>
@@ -18257,7 +18257,7 @@
         <v>49</v>
       </c>
       <c r="F454" s="6">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G454" s="6" t="s">
         <v>11</v>
@@ -18280,7 +18280,7 @@
         <v>49</v>
       </c>
       <c r="F455" s="8">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G455" s="8" t="s">
         <v>11</v>
@@ -18303,7 +18303,7 @@
         <v>49</v>
       </c>
       <c r="F456" s="6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G456" s="6" t="s">
         <v>11</v>
@@ -18326,7 +18326,7 @@
         <v>49</v>
       </c>
       <c r="F457" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G457" s="8" t="s">
         <v>11</v>
@@ -18349,7 +18349,7 @@
         <v>49</v>
       </c>
       <c r="F458" s="6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G458" s="6" t="s">
         <v>11</v>
@@ -18372,7 +18372,7 @@
         <v>49</v>
       </c>
       <c r="F459" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G459" s="8" t="s">
         <v>11</v>
@@ -18395,7 +18395,7 @@
         <v>49</v>
       </c>
       <c r="F460" s="6">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="G460" s="6" t="s">
         <v>11</v>
@@ -18418,7 +18418,7 @@
         <v>49</v>
       </c>
       <c r="F461" s="8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G461" s="8" t="s">
         <v>11</v>
@@ -18441,7 +18441,7 @@
         <v>49</v>
       </c>
       <c r="F462" s="6">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G462" s="6" t="s">
         <v>11</v>
@@ -18464,7 +18464,7 @@
         <v>49</v>
       </c>
       <c r="F463" s="8">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G463" s="8" t="s">
         <v>11</v>
@@ -18487,7 +18487,7 @@
         <v>49</v>
       </c>
       <c r="F464" s="6">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G464" s="6" t="s">
         <v>11</v>
@@ -18510,7 +18510,7 @@
         <v>49</v>
       </c>
       <c r="F465" s="8">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="G465" s="8" t="s">
         <v>11</v>
@@ -18533,7 +18533,7 @@
         <v>49</v>
       </c>
       <c r="F466" s="6">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G466" s="6" t="s">
         <v>11</v>
@@ -18556,7 +18556,7 @@
         <v>49</v>
       </c>
       <c r="F467" s="8">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G467" s="8" t="s">
         <v>11</v>
@@ -18579,7 +18579,7 @@
         <v>49</v>
       </c>
       <c r="F468" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G468" s="6" t="s">
         <v>11</v>
@@ -18602,7 +18602,7 @@
         <v>49</v>
       </c>
       <c r="F469" s="8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G469" s="8" t="s">
         <v>11</v>
@@ -18671,7 +18671,7 @@
         <v>49</v>
       </c>
       <c r="F472" s="6">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G472" s="6" t="s">
         <v>11</v>
@@ -18694,7 +18694,7 @@
         <v>49</v>
       </c>
       <c r="F473" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G473" s="8" t="s">
         <v>11</v>
@@ -18717,7 +18717,7 @@
         <v>49</v>
       </c>
       <c r="F474" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G474" s="6" t="s">
         <v>11</v>
@@ -18763,7 +18763,7 @@
         <v>49</v>
       </c>
       <c r="F476" s="6">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G476" s="6" t="s">
         <v>11</v>
@@ -18786,7 +18786,7 @@
         <v>49</v>
       </c>
       <c r="F477" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G477" s="8" t="s">
         <v>11</v>
@@ -18809,7 +18809,7 @@
         <v>49</v>
       </c>
       <c r="F478" s="6">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G478" s="6" t="s">
         <v>11</v>
@@ -18832,7 +18832,7 @@
         <v>49</v>
       </c>
       <c r="F479" s="8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G479" s="8" t="s">
         <v>11</v>
@@ -18855,7 +18855,7 @@
         <v>49</v>
       </c>
       <c r="F480" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G480" s="6" t="s">
         <v>11</v>
@@ -18878,7 +18878,7 @@
         <v>49</v>
       </c>
       <c r="F481" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G481" s="8" t="s">
         <v>11</v>
@@ -18901,7 +18901,7 @@
         <v>49</v>
       </c>
       <c r="F482" s="6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G482" s="6" t="s">
         <v>11</v>
@@ -18924,7 +18924,7 @@
         <v>49</v>
       </c>
       <c r="F483" s="8">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G483" s="8" t="s">
         <v>11</v>
@@ -18970,7 +18970,7 @@
         <v>49</v>
       </c>
       <c r="F485" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G485" s="8" t="s">
         <v>11</v>
@@ -18993,7 +18993,7 @@
         <v>49</v>
       </c>
       <c r="F486" s="6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G486" s="6" t="s">
         <v>11</v>
@@ -19016,7 +19016,7 @@
         <v>49</v>
       </c>
       <c r="F487" s="8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G487" s="8" t="s">
         <v>11</v>
@@ -19039,7 +19039,7 @@
         <v>49</v>
       </c>
       <c r="F488" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G488" s="6" t="s">
         <v>11</v>
@@ -19062,7 +19062,7 @@
         <v>49</v>
       </c>
       <c r="F489" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G489" s="8" t="s">
         <v>11</v>
@@ -19108,7 +19108,7 @@
         <v>49</v>
       </c>
       <c r="F491" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G491" s="8" t="s">
         <v>11</v>
@@ -19131,7 +19131,7 @@
         <v>49</v>
       </c>
       <c r="F492" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G492" s="6" t="s">
         <v>11</v>
@@ -19154,7 +19154,7 @@
         <v>49</v>
       </c>
       <c r="F493" s="8">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G493" s="8" t="s">
         <v>11</v>
@@ -19177,7 +19177,7 @@
         <v>49</v>
       </c>
       <c r="F494" s="6">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G494" s="6" t="s">
         <v>11</v>
@@ -19200,7 +19200,7 @@
         <v>49</v>
       </c>
       <c r="F495" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G495" s="8" t="s">
         <v>11</v>
@@ -19223,7 +19223,7 @@
         <v>49</v>
       </c>
       <c r="F496" s="6">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G496" s="6" t="s">
         <v>11</v>
@@ -19246,7 +19246,7 @@
         <v>49</v>
       </c>
       <c r="F497" s="8">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G497" s="8" t="s">
         <v>11</v>
@@ -19269,7 +19269,7 @@
         <v>49</v>
       </c>
       <c r="F498" s="6">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G498" s="6" t="s">
         <v>11</v>
@@ -19292,7 +19292,7 @@
         <v>49</v>
       </c>
       <c r="F499" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G499" s="8" t="s">
         <v>11</v>
@@ -19315,7 +19315,7 @@
         <v>49</v>
       </c>
       <c r="F500" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G500" s="6" t="s">
         <v>11</v>
@@ -19361,7 +19361,7 @@
         <v>49</v>
       </c>
       <c r="F502" s="6">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G502" s="6" t="s">
         <v>11</v>
@@ -19384,7 +19384,7 @@
         <v>49</v>
       </c>
       <c r="F503" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G503" s="8" t="s">
         <v>11</v>
@@ -19407,7 +19407,7 @@
         <v>49</v>
       </c>
       <c r="F504" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G504" s="6" t="s">
         <v>11</v>
@@ -19453,7 +19453,7 @@
         <v>49</v>
       </c>
       <c r="F506" s="6">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G506" s="6" t="s">
         <v>11</v>
@@ -19476,7 +19476,7 @@
         <v>49</v>
       </c>
       <c r="F507" s="8">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G507" s="8" t="s">
         <v>11</v>
@@ -19499,7 +19499,7 @@
         <v>49</v>
       </c>
       <c r="F508" s="6">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G508" s="6" t="s">
         <v>11</v>
@@ -19522,7 +19522,7 @@
         <v>49</v>
       </c>
       <c r="F509" s="8">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="G509" s="8" t="s">
         <v>11</v>
@@ -19545,7 +19545,7 @@
         <v>49</v>
       </c>
       <c r="F510" s="6">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G510" s="6" t="s">
         <v>11</v>
@@ -19568,7 +19568,7 @@
         <v>49</v>
       </c>
       <c r="F511" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G511" s="8" t="s">
         <v>11</v>
@@ -19591,7 +19591,7 @@
         <v>49</v>
       </c>
       <c r="F512" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G512" s="6" t="s">
         <v>11</v>
@@ -19614,7 +19614,7 @@
         <v>49</v>
       </c>
       <c r="F513" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G513" s="8" t="s">
         <v>11</v>
@@ -19637,7 +19637,7 @@
         <v>49</v>
       </c>
       <c r="F514" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G514" s="6" t="s">
         <v>11</v>
@@ -19683,7 +19683,7 @@
         <v>49</v>
       </c>
       <c r="F516" s="6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G516" s="6" t="s">
         <v>11</v>
@@ -19706,7 +19706,7 @@
         <v>49</v>
       </c>
       <c r="F517" s="8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G517" s="8" t="s">
         <v>11</v>
@@ -19729,7 +19729,7 @@
         <v>49</v>
       </c>
       <c r="F518" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G518" s="6" t="s">
         <v>11</v>
@@ -19752,7 +19752,7 @@
         <v>49</v>
       </c>
       <c r="F519" s="8">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G519" s="8" t="s">
         <v>11</v>
@@ -19775,7 +19775,7 @@
         <v>49</v>
       </c>
       <c r="F520" s="6">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G520" s="6" t="s">
         <v>11</v>
@@ -19798,7 +19798,7 @@
         <v>49</v>
       </c>
       <c r="F521" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G521" s="8" t="s">
         <v>11</v>
@@ -19867,7 +19867,7 @@
         <v>49</v>
       </c>
       <c r="F524" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G524" s="6" t="s">
         <v>11</v>
@@ -19890,7 +19890,7 @@
         <v>49</v>
       </c>
       <c r="F525" s="8">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G525" s="8" t="s">
         <v>11</v>
@@ -19913,7 +19913,7 @@
         <v>49</v>
       </c>
       <c r="F526" s="6">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G526" s="6" t="s">
         <v>11</v>
@@ -19936,7 +19936,7 @@
         <v>49</v>
       </c>
       <c r="F527" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G527" s="8" t="s">
         <v>11</v>
@@ -19959,7 +19959,7 @@
         <v>49</v>
       </c>
       <c r="F528" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G528" s="6" t="s">
         <v>11</v>
@@ -19982,7 +19982,7 @@
         <v>49</v>
       </c>
       <c r="F529" s="8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G529" s="8" t="s">
         <v>11</v>
@@ -20005,7 +20005,7 @@
         <v>49</v>
       </c>
       <c r="F530" s="6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G530" s="6" t="s">
         <v>11</v>
@@ -20028,7 +20028,7 @@
         <v>49</v>
       </c>
       <c r="F531" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G531" s="8" t="s">
         <v>11</v>
@@ -20051,7 +20051,7 @@
         <v>49</v>
       </c>
       <c r="F532" s="6">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G532" s="6" t="s">
         <v>11</v>
@@ -20074,7 +20074,7 @@
         <v>49</v>
       </c>
       <c r="F533" s="8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G533" s="8" t="s">
         <v>11</v>
@@ -20097,7 +20097,7 @@
         <v>49</v>
       </c>
       <c r="F534" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G534" s="6" t="s">
         <v>11</v>
@@ -20143,7 +20143,7 @@
         <v>49</v>
       </c>
       <c r="F536" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G536" s="6" t="s">
         <v>11</v>
@@ -20189,7 +20189,7 @@
         <v>49</v>
       </c>
       <c r="F538" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G538" s="6" t="s">
         <v>11</v>
@@ -20235,7 +20235,7 @@
         <v>49</v>
       </c>
       <c r="F540" s="6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G540" s="6" t="s">
         <v>11</v>
@@ -20258,7 +20258,7 @@
         <v>49</v>
       </c>
       <c r="F541" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G541" s="8" t="s">
         <v>11</v>
@@ -20281,7 +20281,7 @@
         <v>49</v>
       </c>
       <c r="F542" s="6">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G542" s="6" t="s">
         <v>11</v>
@@ -20304,7 +20304,7 @@
         <v>49</v>
       </c>
       <c r="F543" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G543" s="8" t="s">
         <v>11</v>
@@ -20327,7 +20327,7 @@
         <v>49</v>
       </c>
       <c r="F544" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G544" s="6" t="s">
         <v>11</v>
@@ -20350,7 +20350,7 @@
         <v>49</v>
       </c>
       <c r="F545" s="8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G545" s="8" t="s">
         <v>11</v>
@@ -20373,7 +20373,7 @@
         <v>49</v>
       </c>
       <c r="F546" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G546" s="6" t="s">
         <v>11</v>
@@ -20396,7 +20396,7 @@
         <v>49</v>
       </c>
       <c r="F547" s="8">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G547" s="8" t="s">
         <v>11</v>
@@ -20442,7 +20442,7 @@
         <v>49</v>
       </c>
       <c r="F549" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G549" s="8" t="s">
         <v>11</v>
@@ -20465,7 +20465,7 @@
         <v>49</v>
       </c>
       <c r="F550" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G550" s="6" t="s">
         <v>11</v>
@@ -20488,7 +20488,7 @@
         <v>49</v>
       </c>
       <c r="F551" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G551" s="8" t="s">
         <v>11</v>
@@ -20511,7 +20511,7 @@
         <v>49</v>
       </c>
       <c r="F552" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G552" s="6" t="s">
         <v>11</v>
@@ -20534,7 +20534,7 @@
         <v>49</v>
       </c>
       <c r="F553" s="8">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="G553" s="8" t="s">
         <v>11</v>
@@ -20557,7 +20557,7 @@
         <v>49</v>
       </c>
       <c r="F554" s="6">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G554" s="6" t="s">
         <v>11</v>
@@ -20580,7 +20580,7 @@
         <v>49</v>
       </c>
       <c r="F555" s="8">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G555" s="8" t="s">
         <v>11</v>
@@ -20626,7 +20626,7 @@
         <v>49</v>
       </c>
       <c r="F557" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G557" s="8" t="s">
         <v>11</v>
@@ -20649,7 +20649,7 @@
         <v>49</v>
       </c>
       <c r="F558" s="6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G558" s="6" t="s">
         <v>11</v>
@@ -20672,7 +20672,7 @@
         <v>49</v>
       </c>
       <c r="F559" s="8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G559" s="8" t="s">
         <v>11</v>
@@ -20718,7 +20718,7 @@
         <v>49</v>
       </c>
       <c r="F561" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G561" s="8" t="s">
         <v>11</v>
@@ -20741,7 +20741,7 @@
         <v>49</v>
       </c>
       <c r="F562" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G562" s="6" t="s">
         <v>11</v>
@@ -20764,7 +20764,7 @@
         <v>49</v>
       </c>
       <c r="F563" s="8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G563" s="8" t="s">
         <v>11</v>
@@ -20787,7 +20787,7 @@
         <v>49</v>
       </c>
       <c r="F564" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G564" s="6" t="s">
         <v>11</v>
@@ -20810,7 +20810,7 @@
         <v>49</v>
       </c>
       <c r="F565" s="8">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G565" s="8" t="s">
         <v>11</v>
@@ -20833,7 +20833,7 @@
         <v>49</v>
       </c>
       <c r="F566" s="6">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G566" s="6" t="s">
         <v>11</v>
@@ -20856,7 +20856,7 @@
         <v>49</v>
       </c>
       <c r="F567" s="8">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G567" s="8" t="s">
         <v>11</v>
@@ -20879,7 +20879,7 @@
         <v>49</v>
       </c>
       <c r="F568" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G568" s="6" t="s">
         <v>11</v>
@@ -20902,7 +20902,7 @@
         <v>49</v>
       </c>
       <c r="F569" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G569" s="8" t="s">
         <v>11</v>
@@ -20925,7 +20925,7 @@
         <v>49</v>
       </c>
       <c r="F570" s="6">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G570" s="6" t="s">
         <v>11</v>
@@ -20971,7 +20971,7 @@
         <v>49</v>
       </c>
       <c r="F572" s="6">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="G572" s="6" t="s">
         <v>11</v>
@@ -20994,7 +20994,7 @@
         <v>49</v>
       </c>
       <c r="F573" s="8">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G573" s="8" t="s">
         <v>11</v>
@@ -21017,7 +21017,7 @@
         <v>49</v>
       </c>
       <c r="F574" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G574" s="6" t="s">
         <v>11</v>
@@ -21040,7 +21040,7 @@
         <v>49</v>
       </c>
       <c r="F575" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G575" s="8" t="s">
         <v>11</v>
@@ -21063,7 +21063,7 @@
         <v>49</v>
       </c>
       <c r="F576" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G576" s="6" t="s">
         <v>11</v>
@@ -21086,7 +21086,7 @@
         <v>49</v>
       </c>
       <c r="F577" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G577" s="8" t="s">
         <v>11</v>
@@ -21109,7 +21109,7 @@
         <v>49</v>
       </c>
       <c r="F578" s="6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G578" s="6" t="s">
         <v>11</v>
@@ -21132,7 +21132,7 @@
         <v>49</v>
       </c>
       <c r="F579" s="8">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G579" s="8" t="s">
         <v>11</v>
@@ -21155,7 +21155,7 @@
         <v>49</v>
       </c>
       <c r="F580" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G580" s="6" t="s">
         <v>11</v>
@@ -21178,7 +21178,7 @@
         <v>49</v>
       </c>
       <c r="F581" s="8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G581" s="8" t="s">
         <v>11</v>
@@ -21201,7 +21201,7 @@
         <v>49</v>
       </c>
       <c r="F582" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G582" s="6" t="s">
         <v>11</v>
@@ -21224,7 +21224,7 @@
         <v>49</v>
       </c>
       <c r="F583" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G583" s="8" t="s">
         <v>11</v>
@@ -21247,7 +21247,7 @@
         <v>49</v>
       </c>
       <c r="F584" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G584" s="6" t="s">
         <v>11</v>
@@ -21270,7 +21270,7 @@
         <v>49</v>
       </c>
       <c r="F585" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G585" s="8" t="s">
         <v>11</v>
@@ -21293,7 +21293,7 @@
         <v>49</v>
       </c>
       <c r="F586" s="6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G586" s="6" t="s">
         <v>11</v>
@@ -21316,7 +21316,7 @@
         <v>49</v>
       </c>
       <c r="F587" s="8">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G587" s="8" t="s">
         <v>11</v>
@@ -21339,7 +21339,7 @@
         <v>49</v>
       </c>
       <c r="F588" s="6">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G588" s="6" t="s">
         <v>11</v>
@@ -21362,7 +21362,7 @@
         <v>49</v>
       </c>
       <c r="F589" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G589" s="8" t="s">
         <v>11</v>
@@ -21385,7 +21385,7 @@
         <v>49</v>
       </c>
       <c r="F590" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G590" s="6" t="s">
         <v>11</v>
@@ -21408,7 +21408,7 @@
         <v>49</v>
       </c>
       <c r="F591" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G591" s="8" t="s">
         <v>11</v>
@@ -21431,7 +21431,7 @@
         <v>49</v>
       </c>
       <c r="F592" s="6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G592" s="6" t="s">
         <v>11</v>
@@ -21454,7 +21454,7 @@
         <v>49</v>
       </c>
       <c r="F593" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G593" s="8" t="s">
         <v>11</v>
@@ -21477,7 +21477,7 @@
         <v>49</v>
       </c>
       <c r="F594" s="6">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G594" s="6" t="s">
         <v>11</v>
@@ -21500,7 +21500,7 @@
         <v>49</v>
       </c>
       <c r="F595" s="8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G595" s="8" t="s">
         <v>11</v>
@@ -21523,7 +21523,7 @@
         <v>49</v>
       </c>
       <c r="F596" s="6">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G596" s="6" t="s">
         <v>11</v>
@@ -21546,7 +21546,7 @@
         <v>49</v>
       </c>
       <c r="F597" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G597" s="8" t="s">
         <v>11</v>
@@ -21592,7 +21592,7 @@
         <v>49</v>
       </c>
       <c r="F599" s="8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G599" s="8" t="s">
         <v>11</v>
@@ -21615,7 +21615,7 @@
         <v>49</v>
       </c>
       <c r="F600" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G600" s="6" t="s">
         <v>11</v>
@@ -21661,7 +21661,7 @@
         <v>49</v>
       </c>
       <c r="F602" s="6">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G602" s="6" t="s">
         <v>11</v>
@@ -21684,7 +21684,7 @@
         <v>49</v>
       </c>
       <c r="F603" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G603" s="8" t="s">
         <v>11</v>
@@ -21707,7 +21707,7 @@
         <v>49</v>
       </c>
       <c r="F604" s="6">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G604" s="6" t="s">
         <v>11</v>
@@ -21730,7 +21730,7 @@
         <v>49</v>
       </c>
       <c r="F605" s="8">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G605" s="8" t="s">
         <v>11</v>
@@ -21753,7 +21753,7 @@
         <v>49</v>
       </c>
       <c r="F606" s="6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G606" s="6" t="s">
         <v>11</v>
@@ -21799,7 +21799,7 @@
         <v>49</v>
       </c>
       <c r="F608" s="6">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G608" s="6" t="s">
         <v>11</v>
@@ -21822,7 +21822,7 @@
         <v>49</v>
       </c>
       <c r="F609" s="8">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G609" s="8" t="s">
         <v>11</v>
@@ -21845,7 +21845,7 @@
         <v>49</v>
       </c>
       <c r="F610" s="6">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="G610" s="6" t="s">
         <v>11</v>
@@ -21868,7 +21868,7 @@
         <v>49</v>
       </c>
       <c r="F611" s="8">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="G611" s="8" t="s">
         <v>11</v>
@@ -21891,7 +21891,7 @@
         <v>49</v>
       </c>
       <c r="F612" s="6">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G612" s="6" t="s">
         <v>11</v>
@@ -21914,7 +21914,7 @@
         <v>49</v>
       </c>
       <c r="F613" s="8">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G613" s="8" t="s">
         <v>11</v>
@@ -21960,7 +21960,7 @@
         <v>49</v>
       </c>
       <c r="F615" s="8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G615" s="8" t="s">
         <v>11</v>
@@ -21983,7 +21983,7 @@
         <v>49</v>
       </c>
       <c r="F616" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G616" s="6" t="s">
         <v>11</v>
@@ -22006,7 +22006,7 @@
         <v>49</v>
       </c>
       <c r="F617" s="8">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G617" s="8" t="s">
         <v>11</v>
@@ -22029,7 +22029,7 @@
         <v>49</v>
       </c>
       <c r="F618" s="6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G618" s="6" t="s">
         <v>11</v>
@@ -22052,7 +22052,7 @@
         <v>49</v>
       </c>
       <c r="F619" s="8">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G619" s="8" t="s">
         <v>11</v>
@@ -22075,7 +22075,7 @@
         <v>49</v>
       </c>
       <c r="F620" s="6">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G620" s="6" t="s">
         <v>11</v>
@@ -22098,7 +22098,7 @@
         <v>49</v>
       </c>
       <c r="F621" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G621" s="8" t="s">
         <v>11</v>
@@ -22121,7 +22121,7 @@
         <v>49</v>
       </c>
       <c r="F622" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G622" s="6" t="s">
         <v>11</v>
@@ -22144,7 +22144,7 @@
         <v>49</v>
       </c>
       <c r="F623" s="8">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G623" s="8" t="s">
         <v>11</v>
@@ -22190,7 +22190,7 @@
         <v>49</v>
       </c>
       <c r="F625" s="8">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G625" s="8" t="s">
         <v>11</v>
@@ -22213,7 +22213,7 @@
         <v>49</v>
       </c>
       <c r="F626" s="6">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="G626" s="6" t="s">
         <v>11</v>
@@ -22236,7 +22236,7 @@
         <v>49</v>
       </c>
       <c r="F627" s="8">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G627" s="8" t="s">
         <v>11</v>
@@ -22259,7 +22259,7 @@
         <v>49</v>
       </c>
       <c r="F628" s="6">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G628" s="6" t="s">
         <v>11</v>
@@ -22282,7 +22282,7 @@
         <v>49</v>
       </c>
       <c r="F629" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G629" s="8" t="s">
         <v>11</v>
@@ -22351,7 +22351,7 @@
         <v>49</v>
       </c>
       <c r="F632" s="6">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G632" s="6" t="s">
         <v>11</v>
@@ -22374,7 +22374,7 @@
         <v>49</v>
       </c>
       <c r="F633" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G633" s="8" t="s">
         <v>11</v>
@@ -22397,7 +22397,7 @@
         <v>49</v>
       </c>
       <c r="F634" s="6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G634" s="6" t="s">
         <v>11</v>
@@ -22420,7 +22420,7 @@
         <v>49</v>
       </c>
       <c r="F635" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G635" s="8" t="s">
         <v>11</v>
@@ -22443,7 +22443,7 @@
         <v>49</v>
       </c>
       <c r="F636" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G636" s="6" t="s">
         <v>11</v>
@@ -22466,7 +22466,7 @@
         <v>49</v>
       </c>
       <c r="F637" s="8">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G637" s="8" t="s">
         <v>11</v>
@@ -22489,7 +22489,7 @@
         <v>49</v>
       </c>
       <c r="F638" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G638" s="6" t="s">
         <v>11</v>
@@ -22512,7 +22512,7 @@
         <v>49</v>
       </c>
       <c r="F639" s="8">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G639" s="8" t="s">
         <v>11</v>
@@ -22535,7 +22535,7 @@
         <v>49</v>
       </c>
       <c r="F640" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G640" s="6" t="s">
         <v>11</v>
@@ -22558,7 +22558,7 @@
         <v>49</v>
       </c>
       <c r="F641" s="8">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G641" s="8" t="s">
         <v>11</v>
@@ -22627,7 +22627,7 @@
         <v>49</v>
       </c>
       <c r="F644" s="6">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G644" s="6" t="s">
         <v>11</v>
@@ -22650,7 +22650,7 @@
         <v>49</v>
       </c>
       <c r="F645" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G645" s="8" t="s">
         <v>11</v>
@@ -22696,7 +22696,7 @@
         <v>49</v>
       </c>
       <c r="F647" s="8">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G647" s="8" t="s">
         <v>11</v>
@@ -22719,7 +22719,7 @@
         <v>49</v>
       </c>
       <c r="F648" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G648" s="6" t="s">
         <v>11</v>
@@ -22742,7 +22742,7 @@
         <v>49</v>
       </c>
       <c r="F649" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G649" s="8" t="s">
         <v>11</v>
@@ -22765,7 +22765,7 @@
         <v>49</v>
       </c>
       <c r="F650" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G650" s="6" t="s">
         <v>11</v>
@@ -22788,7 +22788,7 @@
         <v>49</v>
       </c>
       <c r="F651" s="8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G651" s="8" t="s">
         <v>11</v>
@@ -22811,7 +22811,7 @@
         <v>49</v>
       </c>
       <c r="F652" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G652" s="6" t="s">
         <v>11</v>
@@ -22857,7 +22857,7 @@
         <v>49</v>
       </c>
       <c r="F654" s="6">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G654" s="6" t="s">
         <v>11</v>
@@ -22880,7 +22880,7 @@
         <v>49</v>
       </c>
       <c r="F655" s="8">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G655" s="8" t="s">
         <v>11</v>
@@ -22903,7 +22903,7 @@
         <v>49</v>
       </c>
       <c r="F656" s="6">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G656" s="6" t="s">
         <v>11</v>
@@ -22926,7 +22926,7 @@
         <v>49</v>
       </c>
       <c r="F657" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G657" s="8" t="s">
         <v>11</v>
@@ -22949,7 +22949,7 @@
         <v>49</v>
       </c>
       <c r="F658" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G658" s="6" t="s">
         <v>11</v>
@@ -22972,7 +22972,7 @@
         <v>49</v>
       </c>
       <c r="F659" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G659" s="8" t="s">
         <v>11</v>
@@ -22995,7 +22995,7 @@
         <v>49</v>
       </c>
       <c r="F660" s="6">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G660" s="6" t="s">
         <v>11</v>
@@ -23018,7 +23018,7 @@
         <v>49</v>
       </c>
       <c r="F661" s="8">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G661" s="8" t="s">
         <v>11</v>
@@ -23041,7 +23041,7 @@
         <v>49</v>
       </c>
       <c r="F662" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G662" s="6" t="s">
         <v>11</v>
@@ -23064,7 +23064,7 @@
         <v>49</v>
       </c>
       <c r="F663" s="8">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G663" s="8" t="s">
         <v>11</v>
@@ -23110,7 +23110,7 @@
         <v>49</v>
       </c>
       <c r="F665" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G665" s="8" t="s">
         <v>11</v>
@@ -23133,7 +23133,7 @@
         <v>49</v>
       </c>
       <c r="F666" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G666" s="6" t="s">
         <v>11</v>
@@ -23156,7 +23156,7 @@
         <v>49</v>
       </c>
       <c r="F667" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G667" s="8" t="s">
         <v>11</v>
@@ -23179,7 +23179,7 @@
         <v>49</v>
       </c>
       <c r="F668" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G668" s="6" t="s">
         <v>11</v>
@@ -23202,7 +23202,7 @@
         <v>49</v>
       </c>
       <c r="F669" s="8">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G669" s="8" t="s">
         <v>11</v>
@@ -23225,7 +23225,7 @@
         <v>49</v>
       </c>
       <c r="F670" s="6">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="G670" s="6" t="s">
         <v>11</v>
@@ -23248,7 +23248,7 @@
         <v>49</v>
       </c>
       <c r="F671" s="8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G671" s="8" t="s">
         <v>11</v>
@@ -23294,7 +23294,7 @@
         <v>49</v>
       </c>
       <c r="F673" s="8">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G673" s="8" t="s">
         <v>11</v>
@@ -23317,7 +23317,7 @@
         <v>49</v>
       </c>
       <c r="F674" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G674" s="6" t="s">
         <v>11</v>
@@ -23340,7 +23340,7 @@
         <v>49</v>
       </c>
       <c r="F675" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G675" s="8" t="s">
         <v>11</v>
@@ -23363,7 +23363,7 @@
         <v>49</v>
       </c>
       <c r="F676" s="6">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G676" s="6" t="s">
         <v>11</v>
@@ -23386,7 +23386,7 @@
         <v>49</v>
       </c>
       <c r="F677" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G677" s="8" t="s">
         <v>11</v>
@@ -23409,7 +23409,7 @@
         <v>49</v>
       </c>
       <c r="F678" s="6">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="G678" s="6" t="s">
         <v>11</v>
@@ -23432,7 +23432,7 @@
         <v>49</v>
       </c>
       <c r="F679" s="8">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G679" s="8" t="s">
         <v>11</v>
@@ -23455,7 +23455,7 @@
         <v>49</v>
       </c>
       <c r="F680" s="6">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G680" s="6" t="s">
         <v>11</v>
@@ -23478,7 +23478,7 @@
         <v>49</v>
       </c>
       <c r="F681" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G681" s="8" t="s">
         <v>11</v>
@@ -23501,7 +23501,7 @@
         <v>49</v>
       </c>
       <c r="F682" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G682" s="6" t="s">
         <v>11</v>
@@ -23547,7 +23547,7 @@
         <v>49</v>
       </c>
       <c r="F684" s="6">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G684" s="6" t="s">
         <v>11</v>
@@ -23570,7 +23570,7 @@
         <v>49</v>
       </c>
       <c r="F685" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G685" s="8" t="s">
         <v>11</v>
@@ -23616,7 +23616,7 @@
         <v>49</v>
       </c>
       <c r="F687" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G687" s="8" t="s">
         <v>11</v>
@@ -23639,7 +23639,7 @@
         <v>49</v>
       </c>
       <c r="F688" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G688" s="6" t="s">
         <v>11</v>
@@ -23662,7 +23662,7 @@
         <v>49</v>
       </c>
       <c r="F689" s="8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G689" s="8" t="s">
         <v>11</v>
@@ -23685,7 +23685,7 @@
         <v>49</v>
       </c>
       <c r="F690" s="6">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G690" s="6" t="s">
         <v>11</v>
@@ -23754,7 +23754,7 @@
         <v>49</v>
       </c>
       <c r="F693" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G693" s="8" t="s">
         <v>11</v>
@@ -23777,7 +23777,7 @@
         <v>49</v>
       </c>
       <c r="F694" s="6">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G694" s="6" t="s">
         <v>11</v>
@@ -23800,7 +23800,7 @@
         <v>49</v>
       </c>
       <c r="F695" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G695" s="8" t="s">
         <v>11</v>
@@ -23823,7 +23823,7 @@
         <v>49</v>
       </c>
       <c r="F696" s="6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G696" s="6" t="s">
         <v>11</v>
@@ -23846,7 +23846,7 @@
         <v>49</v>
       </c>
       <c r="F697" s="8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G697" s="8" t="s">
         <v>11</v>
@@ -23869,7 +23869,7 @@
         <v>49</v>
       </c>
       <c r="F698" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G698" s="6" t="s">
         <v>11</v>
@@ -23892,7 +23892,7 @@
         <v>49</v>
       </c>
       <c r="F699" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G699" s="8" t="s">
         <v>11</v>
@@ -23915,7 +23915,7 @@
         <v>49</v>
       </c>
       <c r="F700" s="6">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G700" s="6" t="s">
         <v>11</v>
@@ -23938,7 +23938,7 @@
         <v>49</v>
       </c>
       <c r="F701" s="8">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G701" s="8" t="s">
         <v>11</v>
@@ -23961,7 +23961,7 @@
         <v>49</v>
       </c>
       <c r="F702" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G702" s="6" t="s">
         <v>11</v>
@@ -24007,7 +24007,7 @@
         <v>49</v>
       </c>
       <c r="F704" s="6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G704" s="6" t="s">
         <v>11</v>
@@ -24053,7 +24053,7 @@
         <v>49</v>
       </c>
       <c r="F706" s="6">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G706" s="6" t="s">
         <v>11</v>
@@ -24076,7 +24076,7 @@
         <v>49</v>
       </c>
       <c r="F707" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G707" s="8" t="s">
         <v>11</v>
@@ -24099,7 +24099,7 @@
         <v>49</v>
       </c>
       <c r="F708" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G708" s="6" t="s">
         <v>11</v>
@@ -24122,7 +24122,7 @@
         <v>49</v>
       </c>
       <c r="F709" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G709" s="8" t="s">
         <v>11</v>
@@ -24145,7 +24145,7 @@
         <v>49</v>
       </c>
       <c r="F710" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G710" s="6" t="s">
         <v>11</v>
@@ -24168,7 +24168,7 @@
         <v>49</v>
       </c>
       <c r="F711" s="8">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G711" s="8" t="s">
         <v>11</v>
@@ -24191,7 +24191,7 @@
         <v>49</v>
       </c>
       <c r="F712" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G712" s="6" t="s">
         <v>11</v>
@@ -24214,7 +24214,7 @@
         <v>49</v>
       </c>
       <c r="F713" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G713" s="8" t="s">
         <v>11</v>
@@ -24237,7 +24237,7 @@
         <v>49</v>
       </c>
       <c r="F714" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G714" s="6" t="s">
         <v>11</v>
@@ -24260,7 +24260,7 @@
         <v>49</v>
       </c>
       <c r="F715" s="8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G715" s="8" t="s">
         <v>11</v>
@@ -24283,7 +24283,7 @@
         <v>49</v>
       </c>
       <c r="F716" s="6">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G716" s="6" t="s">
         <v>11</v>
@@ -24329,7 +24329,7 @@
         <v>49</v>
       </c>
       <c r="F718" s="6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G718" s="6" t="s">
         <v>11</v>
@@ -24352,7 +24352,7 @@
         <v>49</v>
       </c>
       <c r="F719" s="8">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G719" s="8" t="s">
         <v>11</v>
@@ -24375,7 +24375,7 @@
         <v>49</v>
       </c>
       <c r="F720" s="6">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G720" s="6" t="s">
         <v>11</v>
@@ -24398,7 +24398,7 @@
         <v>49</v>
       </c>
       <c r="F721" s="8">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G721" s="8" t="s">
         <v>11</v>
@@ -24421,7 +24421,7 @@
         <v>49</v>
       </c>
       <c r="F722" s="6">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G722" s="6" t="s">
         <v>11</v>
@@ -24444,7 +24444,7 @@
         <v>49</v>
       </c>
       <c r="F723" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G723" s="8" t="s">
         <v>11</v>
@@ -24467,7 +24467,7 @@
         <v>49</v>
       </c>
       <c r="F724" s="6">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G724" s="6" t="s">
         <v>11</v>
@@ -24490,7 +24490,7 @@
         <v>49</v>
       </c>
       <c r="F725" s="8">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G725" s="8" t="s">
         <v>11</v>
@@ -24513,7 +24513,7 @@
         <v>49</v>
       </c>
       <c r="F726" s="6">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G726" s="6" t="s">
         <v>11</v>
@@ -24559,7 +24559,7 @@
         <v>49</v>
       </c>
       <c r="F728" s="6">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G728" s="6" t="s">
         <v>11</v>
@@ -24582,7 +24582,7 @@
         <v>49</v>
       </c>
       <c r="F729" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G729" s="8" t="s">
         <v>11</v>
@@ -24651,7 +24651,7 @@
         <v>49</v>
       </c>
       <c r="F732" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G732" s="6" t="s">
         <v>11</v>
@@ -24674,7 +24674,7 @@
         <v>49</v>
       </c>
       <c r="F733" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G733" s="8" t="s">
         <v>11</v>
@@ -24697,7 +24697,7 @@
         <v>49</v>
       </c>
       <c r="F734" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G734" s="6" t="s">
         <v>11</v>
@@ -24720,7 +24720,7 @@
         <v>49</v>
       </c>
       <c r="F735" s="8">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G735" s="8" t="s">
         <v>11</v>
@@ -24766,7 +24766,7 @@
         <v>49</v>
       </c>
       <c r="F737" s="8">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G737" s="8" t="s">
         <v>11</v>
@@ -24789,7 +24789,7 @@
         <v>49</v>
       </c>
       <c r="F738" s="6">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G738" s="6" t="s">
         <v>11</v>
@@ -24812,7 +24812,7 @@
         <v>49</v>
       </c>
       <c r="F739" s="8">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G739" s="8" t="s">
         <v>11</v>
@@ -24835,7 +24835,7 @@
         <v>49</v>
       </c>
       <c r="F740" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G740" s="6" t="s">
         <v>11</v>
@@ -24858,7 +24858,7 @@
         <v>49</v>
       </c>
       <c r="F741" s="8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G741" s="8" t="s">
         <v>11</v>
@@ -24881,7 +24881,7 @@
         <v>49</v>
       </c>
       <c r="F742" s="6">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G742" s="6" t="s">
         <v>11</v>
@@ -24950,7 +24950,7 @@
         <v>49</v>
       </c>
       <c r="F745" s="8">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G745" s="8" t="s">
         <v>11</v>
@@ -24973,7 +24973,7 @@
         <v>49</v>
       </c>
       <c r="F746" s="6">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G746" s="6" t="s">
         <v>11</v>
@@ -24996,7 +24996,7 @@
         <v>49</v>
       </c>
       <c r="F747" s="8">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G747" s="8" t="s">
         <v>11</v>
@@ -25019,7 +25019,7 @@
         <v>49</v>
       </c>
       <c r="F748" s="6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G748" s="6" t="s">
         <v>11</v>
@@ -25042,7 +25042,7 @@
         <v>49</v>
       </c>
       <c r="F749" s="8">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G749" s="8" t="s">
         <v>11</v>
@@ -25065,7 +25065,7 @@
         <v>49</v>
       </c>
       <c r="F750" s="6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G750" s="6" t="s">
         <v>11</v>
@@ -25088,7 +25088,7 @@
         <v>49</v>
       </c>
       <c r="F751" s="8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G751" s="8" t="s">
         <v>11</v>
@@ -25157,7 +25157,7 @@
         <v>49</v>
       </c>
       <c r="F754" s="6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G754" s="6" t="s">
         <v>11</v>
@@ -25203,7 +25203,7 @@
         <v>49</v>
       </c>
       <c r="F756" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G756" s="6" t="s">
         <v>11</v>
@@ -25226,7 +25226,7 @@
         <v>49</v>
       </c>
       <c r="F757" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G757" s="8" t="s">
         <v>11</v>
@@ -25249,7 +25249,7 @@
         <v>49</v>
       </c>
       <c r="F758" s="6">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G758" s="6" t="s">
         <v>11</v>
@@ -25295,7 +25295,7 @@
         <v>49</v>
       </c>
       <c r="F760" s="6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G760" s="6" t="s">
         <v>11</v>
@@ -25318,7 +25318,7 @@
         <v>49</v>
       </c>
       <c r="F761" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G761" s="8" t="s">
         <v>11</v>
@@ -25364,7 +25364,7 @@
         <v>49</v>
       </c>
       <c r="F763" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G763" s="8" t="s">
         <v>11</v>
@@ -25387,7 +25387,7 @@
         <v>49</v>
       </c>
       <c r="F764" s="6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G764" s="6" t="s">
         <v>11</v>
@@ -25410,7 +25410,7 @@
         <v>49</v>
       </c>
       <c r="F765" s="8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G765" s="8" t="s">
         <v>11</v>
@@ -25433,7 +25433,7 @@
         <v>49</v>
       </c>
       <c r="F766" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G766" s="6" t="s">
         <v>11</v>
@@ -25456,7 +25456,7 @@
         <v>49</v>
       </c>
       <c r="F767" s="8">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G767" s="8" t="s">
         <v>11</v>
@@ -25479,7 +25479,7 @@
         <v>49</v>
       </c>
       <c r="F768" s="6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G768" s="6" t="s">
         <v>11</v>
@@ -25502,7 +25502,7 @@
         <v>49</v>
       </c>
       <c r="F769" s="8">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G769" s="8" t="s">
         <v>11</v>
@@ -25525,7 +25525,7 @@
         <v>49</v>
       </c>
       <c r="F770" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G770" s="6" t="s">
         <v>11</v>
@@ -25571,7 +25571,7 @@
         <v>49</v>
       </c>
       <c r="F772" s="6">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G772" s="6" t="s">
         <v>11</v>
@@ -25594,7 +25594,7 @@
         <v>49</v>
       </c>
       <c r="F773" s="8">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="G773" s="8" t="s">
         <v>11</v>
@@ -25617,7 +25617,7 @@
         <v>49</v>
       </c>
       <c r="F774" s="6">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G774" s="6" t="s">
         <v>11</v>
@@ -25640,7 +25640,7 @@
         <v>49</v>
       </c>
       <c r="F775" s="8">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G775" s="8" t="s">
         <v>11</v>
@@ -25663,7 +25663,7 @@
         <v>49</v>
       </c>
       <c r="F776" s="6">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G776" s="6" t="s">
         <v>11</v>
@@ -25686,7 +25686,7 @@
         <v>49</v>
       </c>
       <c r="F777" s="8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G777" s="8" t="s">
         <v>11</v>
@@ -25709,7 +25709,7 @@
         <v>49</v>
       </c>
       <c r="F778" s="6">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G778" s="6" t="s">
         <v>11</v>
@@ -25732,7 +25732,7 @@
         <v>49</v>
       </c>
       <c r="F779" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G779" s="8" t="s">
         <v>11</v>
@@ -25755,7 +25755,7 @@
         <v>49</v>
       </c>
       <c r="F780" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G780" s="6" t="s">
         <v>11</v>
@@ -25801,7 +25801,7 @@
         <v>49</v>
       </c>
       <c r="F782" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G782" s="6" t="s">
         <v>11</v>
@@ -25824,7 +25824,7 @@
         <v>49</v>
       </c>
       <c r="F783" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G783" s="8" t="s">
         <v>11</v>
@@ -25847,7 +25847,7 @@
         <v>49</v>
       </c>
       <c r="F784" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G784" s="6" t="s">
         <v>11</v>
@@ -25870,7 +25870,7 @@
         <v>49</v>
       </c>
       <c r="F785" s="8">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G785" s="8" t="s">
         <v>11</v>
@@ -25893,7 +25893,7 @@
         <v>49</v>
       </c>
       <c r="F786" s="6">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G786" s="6" t="s">
         <v>11</v>
@@ -25962,7 +25962,7 @@
         <v>49</v>
       </c>
       <c r="F789" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G789" s="8" t="s">
         <v>11</v>
@@ -25985,7 +25985,7 @@
         <v>49</v>
       </c>
       <c r="F790" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G790" s="6" t="s">
         <v>11</v>
@@ -26008,7 +26008,7 @@
         <v>49</v>
       </c>
       <c r="F791" s="8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G791" s="8" t="s">
         <v>11</v>
@@ -26031,7 +26031,7 @@
         <v>49</v>
       </c>
       <c r="F792" s="6">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G792" s="6" t="s">
         <v>11</v>
@@ -26077,7 +26077,7 @@
         <v>49</v>
       </c>
       <c r="F794" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G794" s="6" t="s">
         <v>11</v>
@@ -26123,7 +26123,7 @@
         <v>49</v>
       </c>
       <c r="F796" s="6">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G796" s="6" t="s">
         <v>11</v>
@@ -26146,7 +26146,7 @@
         <v>49</v>
       </c>
       <c r="F797" s="8">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G797" s="8" t="s">
         <v>11</v>
@@ -26169,7 +26169,7 @@
         <v>49</v>
       </c>
       <c r="F798" s="6">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G798" s="6" t="s">
         <v>11</v>
@@ -26192,7 +26192,7 @@
         <v>49</v>
       </c>
       <c r="F799" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G799" s="8" t="s">
         <v>11</v>
@@ -26238,7 +26238,7 @@
         <v>49</v>
       </c>
       <c r="F801" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G801" s="8" t="s">
         <v>11</v>
@@ -26261,7 +26261,7 @@
         <v>49</v>
       </c>
       <c r="F802" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G802" s="6" t="s">
         <v>11</v>
@@ -26284,7 +26284,7 @@
         <v>49</v>
       </c>
       <c r="F803" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G803" s="8" t="s">
         <v>11</v>
@@ -26307,7 +26307,7 @@
         <v>49</v>
       </c>
       <c r="F804" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G804" s="6" t="s">
         <v>11</v>
@@ -26353,7 +26353,7 @@
         <v>49</v>
       </c>
       <c r="F806" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G806" s="6" t="s">
         <v>11</v>
@@ -26376,7 +26376,7 @@
         <v>49</v>
       </c>
       <c r="F807" s="8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G807" s="8" t="s">
         <v>11</v>
@@ -26399,7 +26399,7 @@
         <v>49</v>
       </c>
       <c r="F808" s="6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G808" s="6" t="s">
         <v>11</v>
@@ -26422,7 +26422,7 @@
         <v>49</v>
       </c>
       <c r="F809" s="8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G809" s="8" t="s">
         <v>11</v>
@@ -26445,7 +26445,7 @@
         <v>49</v>
       </c>
       <c r="F810" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G810" s="6" t="s">
         <v>11</v>
@@ -26468,7 +26468,7 @@
         <v>49</v>
       </c>
       <c r="F811" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G811" s="8" t="s">
         <v>11</v>
@@ -26514,7 +26514,7 @@
         <v>49</v>
       </c>
       <c r="F813" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G813" s="8" t="s">
         <v>11</v>
@@ -26537,7 +26537,7 @@
         <v>49</v>
       </c>
       <c r="F814" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G814" s="6" t="s">
         <v>11</v>
@@ -26560,7 +26560,7 @@
         <v>49</v>
       </c>
       <c r="F815" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G815" s="8" t="s">
         <v>11</v>
@@ -26583,7 +26583,7 @@
         <v>49</v>
       </c>
       <c r="F816" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G816" s="6" t="s">
         <v>11</v>
@@ -26606,7 +26606,7 @@
         <v>49</v>
       </c>
       <c r="F817" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G817" s="8" t="s">
         <v>11</v>
@@ -26629,7 +26629,7 @@
         <v>49</v>
       </c>
       <c r="F818" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G818" s="6" t="s">
         <v>11</v>
@@ -26652,7 +26652,7 @@
         <v>49</v>
       </c>
       <c r="F819" s="8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G819" s="8" t="s">
         <v>11</v>
@@ -26675,7 +26675,7 @@
         <v>49</v>
       </c>
       <c r="F820" s="6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G820" s="6" t="s">
         <v>11</v>
@@ -26698,7 +26698,7 @@
         <v>49</v>
       </c>
       <c r="F821" s="8">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G821" s="8" t="s">
         <v>11</v>
@@ -26744,7 +26744,7 @@
         <v>49</v>
       </c>
       <c r="F823" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G823" s="8" t="s">
         <v>11</v>
@@ -26790,7 +26790,7 @@
         <v>49</v>
       </c>
       <c r="F825" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G825" s="8" t="s">
         <v>11</v>
@@ -26813,7 +26813,7 @@
         <v>49</v>
       </c>
       <c r="F826" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G826" s="6" t="s">
         <v>11</v>
@@ -26836,7 +26836,7 @@
         <v>49</v>
       </c>
       <c r="F827" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G827" s="8" t="s">
         <v>11</v>
@@ -26859,7 +26859,7 @@
         <v>49</v>
       </c>
       <c r="F828" s="6">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G828" s="6" t="s">
         <v>11</v>
@@ -26882,7 +26882,7 @@
         <v>49</v>
       </c>
       <c r="F829" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G829" s="8" t="s">
         <v>11</v>
@@ -26905,7 +26905,7 @@
         <v>49</v>
       </c>
       <c r="F830" s="6">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G830" s="6" t="s">
         <v>11</v>
@@ -26928,7 +26928,7 @@
         <v>49</v>
       </c>
       <c r="F831" s="8">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="G831" s="8" t="s">
         <v>11</v>
@@ -26951,7 +26951,7 @@
         <v>49</v>
       </c>
       <c r="F832" s="6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G832" s="6" t="s">
         <v>11</v>
@@ -26974,7 +26974,7 @@
         <v>49</v>
       </c>
       <c r="F833" s="8">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G833" s="8" t="s">
         <v>11</v>
@@ -26997,7 +26997,7 @@
         <v>49</v>
       </c>
       <c r="F834" s="6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G834" s="6" t="s">
         <v>11</v>
@@ -27020,7 +27020,7 @@
         <v>49</v>
       </c>
       <c r="F835" s="8">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G835" s="8" t="s">
         <v>11</v>
@@ -27043,7 +27043,7 @@
         <v>49</v>
       </c>
       <c r="F836" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G836" s="6" t="s">
         <v>11</v>
@@ -27066,7 +27066,7 @@
         <v>49</v>
       </c>
       <c r="F837" s="8">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G837" s="8" t="s">
         <v>11</v>
@@ -27089,7 +27089,7 @@
         <v>49</v>
       </c>
       <c r="F838" s="6">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G838" s="6" t="s">
         <v>11</v>
@@ -27158,7 +27158,7 @@
         <v>49</v>
       </c>
       <c r="F841" s="8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G841" s="8" t="s">
         <v>11</v>
@@ -27181,7 +27181,7 @@
         <v>49</v>
       </c>
       <c r="F842" s="6">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="G842" s="6" t="s">
         <v>11</v>
@@ -27204,7 +27204,7 @@
         <v>49</v>
       </c>
       <c r="F843" s="8">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G843" s="8" t="s">
         <v>11</v>
@@ -27227,7 +27227,7 @@
         <v>49</v>
       </c>
       <c r="F844" s="6">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G844" s="6" t="s">
         <v>11</v>
@@ -27250,7 +27250,7 @@
         <v>49</v>
       </c>
       <c r="F845" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G845" s="8" t="s">
         <v>11</v>
@@ -27296,7 +27296,7 @@
         <v>49</v>
       </c>
       <c r="F847" s="8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G847" s="8" t="s">
         <v>11</v>
@@ -27319,7 +27319,7 @@
         <v>49</v>
       </c>
       <c r="F848" s="6">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G848" s="6" t="s">
         <v>11</v>
@@ -27342,7 +27342,7 @@
         <v>49</v>
       </c>
       <c r="F849" s="8">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G849" s="8" t="s">
         <v>11</v>
@@ -27365,7 +27365,7 @@
         <v>49</v>
       </c>
       <c r="F850" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G850" s="6" t="s">
         <v>11</v>
@@ -27388,7 +27388,7 @@
         <v>49</v>
       </c>
       <c r="F851" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G851" s="8" t="s">
         <v>11</v>
@@ -27411,7 +27411,7 @@
         <v>49</v>
       </c>
       <c r="F852" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G852" s="6" t="s">
         <v>11</v>
@@ -27434,7 +27434,7 @@
         <v>49</v>
       </c>
       <c r="F853" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G853" s="8" t="s">
         <v>11</v>
@@ -27457,7 +27457,7 @@
         <v>49</v>
       </c>
       <c r="F854" s="6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G854" s="6" t="s">
         <v>11</v>
@@ -27480,7 +27480,7 @@
         <v>49</v>
       </c>
       <c r="F855" s="8">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="G855" s="8" t="s">
         <v>11</v>
@@ -27503,7 +27503,7 @@
         <v>49</v>
       </c>
       <c r="F856" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G856" s="6" t="s">
         <v>11</v>
@@ -27549,7 +27549,7 @@
         <v>49</v>
       </c>
       <c r="F858" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G858" s="6" t="s">
         <v>11</v>
@@ -27572,7 +27572,7 @@
         <v>49</v>
       </c>
       <c r="F859" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G859" s="8" t="s">
         <v>11</v>
@@ -27595,7 +27595,7 @@
         <v>49</v>
       </c>
       <c r="F860" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G860" s="6" t="s">
         <v>11</v>
@@ -27618,7 +27618,7 @@
         <v>49</v>
       </c>
       <c r="F861" s="8">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G861" s="8" t="s">
         <v>11</v>
@@ -27641,7 +27641,7 @@
         <v>49</v>
       </c>
       <c r="F862" s="6">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G862" s="6" t="s">
         <v>11</v>
@@ -27687,7 +27687,7 @@
         <v>49</v>
       </c>
       <c r="F864" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G864" s="6" t="s">
         <v>11</v>
@@ -27710,7 +27710,7 @@
         <v>49</v>
       </c>
       <c r="F865" s="8">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G865" s="8" t="s">
         <v>11</v>
@@ -27733,7 +27733,7 @@
         <v>49</v>
       </c>
       <c r="F866" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G866" s="6" t="s">
         <v>11</v>
@@ -27802,7 +27802,7 @@
         <v>49</v>
       </c>
       <c r="F869" s="8">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G869" s="8" t="s">
         <v>11</v>
@@ -27825,7 +27825,7 @@
         <v>49</v>
       </c>
       <c r="F870" s="6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G870" s="6" t="s">
         <v>11</v>
@@ -27871,7 +27871,7 @@
         <v>49</v>
       </c>
       <c r="F872" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G872" s="6" t="s">
         <v>11</v>
@@ -27894,7 +27894,7 @@
         <v>49</v>
       </c>
       <c r="F873" s="8">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G873" s="8" t="s">
         <v>11</v>
@@ -27917,7 +27917,7 @@
         <v>49</v>
       </c>
       <c r="F874" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G874" s="6" t="s">
         <v>11</v>
@@ -27963,7 +27963,7 @@
         <v>49</v>
       </c>
       <c r="F876" s="6">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="G876" s="6" t="s">
         <v>11</v>
@@ -27986,7 +27986,7 @@
         <v>49</v>
       </c>
       <c r="F877" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G877" s="8" t="s">
         <v>11</v>
@@ -28009,7 +28009,7 @@
         <v>49</v>
       </c>
       <c r="F878" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G878" s="6" t="s">
         <v>11</v>
@@ -28032,7 +28032,7 @@
         <v>49</v>
       </c>
       <c r="F879" s="8">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G879" s="8" t="s">
         <v>11</v>
@@ -28055,7 +28055,7 @@
         <v>49</v>
       </c>
       <c r="F880" s="6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G880" s="6" t="s">
         <v>11</v>
@@ -28078,7 +28078,7 @@
         <v>49</v>
       </c>
       <c r="F881" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G881" s="8" t="s">
         <v>11</v>
@@ -28124,7 +28124,7 @@
         <v>49</v>
       </c>
       <c r="F883" s="8">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G883" s="8" t="s">
         <v>11</v>
@@ -28147,7 +28147,7 @@
         <v>49</v>
       </c>
       <c r="F884" s="6">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G884" s="6" t="s">
         <v>11</v>
@@ -28170,7 +28170,7 @@
         <v>49</v>
       </c>
       <c r="F885" s="8">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G885" s="8" t="s">
         <v>11</v>
@@ -28193,7 +28193,7 @@
         <v>49</v>
       </c>
       <c r="F886" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G886" s="6" t="s">
         <v>11</v>
@@ -28216,7 +28216,7 @@
         <v>49</v>
       </c>
       <c r="F887" s="8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G887" s="8" t="s">
         <v>11</v>
@@ -28285,7 +28285,7 @@
         <v>49</v>
       </c>
       <c r="F890" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G890" s="6" t="s">
         <v>11</v>
@@ -28308,7 +28308,7 @@
         <v>49</v>
       </c>
       <c r="F891" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G891" s="8" t="s">
         <v>11</v>
@@ -28331,7 +28331,7 @@
         <v>49</v>
       </c>
       <c r="F892" s="6">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G892" s="6" t="s">
         <v>11</v>
@@ -28354,7 +28354,7 @@
         <v>49</v>
       </c>
       <c r="F893" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G893" s="8" t="s">
         <v>11</v>
@@ -28400,7 +28400,7 @@
         <v>49</v>
       </c>
       <c r="F895" s="8">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G895" s="8" t="s">
         <v>11</v>
@@ -28423,7 +28423,7 @@
         <v>49</v>
       </c>
       <c r="F896" s="6">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G896" s="6" t="s">
         <v>11</v>
@@ -28446,7 +28446,7 @@
         <v>49</v>
       </c>
       <c r="F897" s="8">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G897" s="8" t="s">
         <v>11</v>
@@ -28469,7 +28469,7 @@
         <v>49</v>
       </c>
       <c r="F898" s="6">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G898" s="6" t="s">
         <v>11</v>
@@ -28492,7 +28492,7 @@
         <v>49</v>
       </c>
       <c r="F899" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G899" s="8" t="s">
         <v>11</v>
@@ -28515,7 +28515,7 @@
         <v>49</v>
       </c>
       <c r="F900" s="6">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="G900" s="6" t="s">
         <v>11</v>
@@ -28561,7 +28561,7 @@
         <v>49</v>
       </c>
       <c r="F902" s="6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G902" s="6" t="s">
         <v>11</v>
@@ -28584,7 +28584,7 @@
         <v>49</v>
       </c>
       <c r="F903" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G903" s="8" t="s">
         <v>11</v>
@@ -28607,7 +28607,7 @@
         <v>49</v>
       </c>
       <c r="F904" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G904" s="6" t="s">
         <v>11</v>
@@ -28653,7 +28653,7 @@
         <v>49</v>
       </c>
       <c r="F906" s="6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G906" s="6" t="s">
         <v>11</v>
@@ -28676,7 +28676,7 @@
         <v>49</v>
       </c>
       <c r="F907" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G907" s="8" t="s">
         <v>11</v>
@@ -28699,7 +28699,7 @@
         <v>49</v>
       </c>
       <c r="F908" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G908" s="6" t="s">
         <v>11</v>
@@ -28722,7 +28722,7 @@
         <v>49</v>
       </c>
       <c r="F909" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G909" s="8" t="s">
         <v>11</v>
@@ -28745,7 +28745,7 @@
         <v>49</v>
       </c>
       <c r="F910" s="6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G910" s="6" t="s">
         <v>11</v>
@@ -28768,7 +28768,7 @@
         <v>49</v>
       </c>
       <c r="F911" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G911" s="8" t="s">
         <v>11</v>
@@ -28791,7 +28791,7 @@
         <v>49</v>
       </c>
       <c r="F912" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G912" s="6" t="s">
         <v>11</v>
@@ -28814,7 +28814,7 @@
         <v>49</v>
       </c>
       <c r="F913" s="8">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="G913" s="8" t="s">
         <v>11</v>
@@ -28860,7 +28860,7 @@
         <v>49</v>
       </c>
       <c r="F915" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G915" s="8" t="s">
         <v>11</v>
@@ -28883,7 +28883,7 @@
         <v>49</v>
       </c>
       <c r="F916" s="6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G916" s="6" t="s">
         <v>11</v>
@@ -28906,7 +28906,7 @@
         <v>49</v>
       </c>
       <c r="F917" s="8">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G917" s="8" t="s">
         <v>11</v>
@@ -28929,7 +28929,7 @@
         <v>49</v>
       </c>
       <c r="F918" s="6">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G918" s="6" t="s">
         <v>11</v>
@@ -28975,7 +28975,7 @@
         <v>49</v>
       </c>
       <c r="F920" s="6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G920" s="6" t="s">
         <v>11</v>
@@ -28998,7 +28998,7 @@
         <v>49</v>
       </c>
       <c r="F921" s="8">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G921" s="8" t="s">
         <v>11</v>
@@ -29021,7 +29021,7 @@
         <v>49</v>
       </c>
       <c r="F922" s="6">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G922" s="6" t="s">
         <v>11</v>
@@ -29044,7 +29044,7 @@
         <v>49</v>
       </c>
       <c r="F923" s="8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G923" s="8" t="s">
         <v>11</v>
@@ -29067,7 +29067,7 @@
         <v>49</v>
       </c>
       <c r="F924" s="6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G924" s="6" t="s">
         <v>11</v>
@@ -29090,7 +29090,7 @@
         <v>49</v>
       </c>
       <c r="F925" s="8">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="G925" s="8" t="s">
         <v>11</v>
@@ -29113,7 +29113,7 @@
         <v>49</v>
       </c>
       <c r="F926" s="6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G926" s="6" t="s">
         <v>11</v>
@@ -29136,7 +29136,7 @@
         <v>49</v>
       </c>
       <c r="F927" s="8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G927" s="8" t="s">
         <v>11</v>
@@ -29159,7 +29159,7 @@
         <v>49</v>
       </c>
       <c r="F928" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G928" s="6" t="s">
         <v>11</v>
@@ -29182,7 +29182,7 @@
         <v>49</v>
       </c>
       <c r="F929" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G929" s="8" t="s">
         <v>11</v>
@@ -29205,7 +29205,7 @@
         <v>49</v>
       </c>
       <c r="F930" s="6">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G930" s="6" t="s">
         <v>11</v>
@@ -29251,7 +29251,7 @@
         <v>49</v>
       </c>
       <c r="F932" s="6">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="G932" s="6" t="s">
         <v>11</v>
@@ -29274,7 +29274,7 @@
         <v>49</v>
       </c>
       <c r="F933" s="8">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G933" s="8" t="s">
         <v>11</v>
@@ -29297,7 +29297,7 @@
         <v>49</v>
       </c>
       <c r="F934" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G934" s="6" t="s">
         <v>11</v>
@@ -29320,7 +29320,7 @@
         <v>49</v>
       </c>
       <c r="F935" s="8">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G935" s="8" t="s">
         <v>11</v>
@@ -29343,7 +29343,7 @@
         <v>49</v>
       </c>
       <c r="F936" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G936" s="6" t="s">
         <v>11</v>
@@ -29389,7 +29389,7 @@
         <v>49</v>
       </c>
       <c r="F938" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G938" s="6" t="s">
         <v>11</v>
@@ -29412,7 +29412,7 @@
         <v>49</v>
       </c>
       <c r="F939" s="8">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G939" s="8" t="s">
         <v>11</v>
@@ -29458,7 +29458,7 @@
         <v>49</v>
       </c>
       <c r="F941" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G941" s="8" t="s">
         <v>11</v>
@@ -29481,7 +29481,7 @@
         <v>49</v>
       </c>
       <c r="F942" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G942" s="6" t="s">
         <v>11</v>
@@ -29504,7 +29504,7 @@
         <v>49</v>
       </c>
       <c r="F943" s="8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G943" s="8" t="s">
         <v>11</v>
@@ -29527,7 +29527,7 @@
         <v>49</v>
       </c>
       <c r="F944" s="6">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G944" s="6" t="s">
         <v>11</v>
@@ -29573,7 +29573,7 @@
         <v>49</v>
       </c>
       <c r="F946" s="6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G946" s="6" t="s">
         <v>11</v>
@@ -29596,7 +29596,7 @@
         <v>49</v>
       </c>
       <c r="F947" s="8">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G947" s="8" t="s">
         <v>11</v>
@@ -29619,7 +29619,7 @@
         <v>49</v>
       </c>
       <c r="F948" s="6">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G948" s="6" t="s">
         <v>11</v>
@@ -29642,7 +29642,7 @@
         <v>49</v>
       </c>
       <c r="F949" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G949" s="8" t="s">
         <v>11</v>
@@ -29688,7 +29688,7 @@
         <v>49</v>
       </c>
       <c r="F951" s="8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G951" s="8" t="s">
         <v>11</v>
@@ -29734,7 +29734,7 @@
         <v>49</v>
       </c>
       <c r="F953" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G953" s="8" t="s">
         <v>11</v>
@@ -29780,7 +29780,7 @@
         <v>49</v>
       </c>
       <c r="F955" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G955" s="8" t="s">
         <v>11</v>
@@ -29803,7 +29803,7 @@
         <v>49</v>
       </c>
       <c r="F956" s="6">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G956" s="6" t="s">
         <v>11</v>
@@ -29826,7 +29826,7 @@
         <v>49</v>
       </c>
       <c r="F957" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G957" s="8" t="s">
         <v>11</v>
@@ -29849,7 +29849,7 @@
         <v>49</v>
       </c>
       <c r="F958" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G958" s="6" t="s">
         <v>11</v>
@@ -29872,7 +29872,7 @@
         <v>49</v>
       </c>
       <c r="F959" s="8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G959" s="8" t="s">
         <v>11</v>
@@ -29895,7 +29895,7 @@
         <v>49</v>
       </c>
       <c r="F960" s="6">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G960" s="6" t="s">
         <v>11</v>
@@ -29918,7 +29918,7 @@
         <v>49</v>
       </c>
       <c r="F961" s="8">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G961" s="8" t="s">
         <v>11</v>
@@ -29941,7 +29941,7 @@
         <v>49</v>
       </c>
       <c r="F962" s="6">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G962" s="6" t="s">
         <v>11</v>
@@ -29964,7 +29964,7 @@
         <v>49</v>
       </c>
       <c r="F963" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G963" s="8" t="s">
         <v>11</v>
@@ -29987,7 +29987,7 @@
         <v>49</v>
       </c>
       <c r="F964" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G964" s="6" t="s">
         <v>11</v>
@@ -30010,7 +30010,7 @@
         <v>49</v>
       </c>
       <c r="F965" s="8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G965" s="8" t="s">
         <v>11</v>
@@ -30056,7 +30056,7 @@
         <v>49</v>
       </c>
       <c r="F967" s="8">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G967" s="8" t="s">
         <v>11</v>
@@ -30079,7 +30079,7 @@
         <v>49</v>
       </c>
       <c r="F968" s="6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G968" s="6" t="s">
         <v>11</v>
@@ -30102,7 +30102,7 @@
         <v>49</v>
       </c>
       <c r="F969" s="8">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G969" s="8" t="s">
         <v>11</v>
@@ -30194,7 +30194,7 @@
         <v>49</v>
       </c>
       <c r="F973" s="8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G973" s="8" t="s">
         <v>11</v>
@@ -30217,7 +30217,7 @@
         <v>49</v>
       </c>
       <c r="F974" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G974" s="6" t="s">
         <v>11</v>
@@ -30286,7 +30286,7 @@
         <v>49</v>
       </c>
       <c r="F977" s="8">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G977" s="8" t="s">
         <v>11</v>
@@ -30309,7 +30309,7 @@
         <v>49</v>
       </c>
       <c r="F978" s="6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G978" s="6" t="s">
         <v>11</v>
@@ -30332,7 +30332,7 @@
         <v>49</v>
       </c>
       <c r="F979" s="8">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G979" s="8" t="s">
         <v>11</v>
@@ -30355,7 +30355,7 @@
         <v>49</v>
       </c>
       <c r="F980" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G980" s="6" t="s">
         <v>11</v>
@@ -30378,7 +30378,7 @@
         <v>49</v>
       </c>
       <c r="F981" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G981" s="8" t="s">
         <v>11</v>
@@ -30424,7 +30424,7 @@
         <v>49</v>
       </c>
       <c r="F983" s="8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G983" s="8" t="s">
         <v>11</v>
@@ -30447,7 +30447,7 @@
         <v>49</v>
       </c>
       <c r="F984" s="6">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G984" s="6" t="s">
         <v>11</v>
@@ -30470,7 +30470,7 @@
         <v>49</v>
       </c>
       <c r="F985" s="8">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G985" s="8" t="s">
         <v>11</v>
@@ -30493,7 +30493,7 @@
         <v>49</v>
       </c>
       <c r="F986" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G986" s="6" t="s">
         <v>11</v>
@@ -30539,7 +30539,7 @@
         <v>49</v>
       </c>
       <c r="F988" s="6">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G988" s="6" t="s">
         <v>11</v>
@@ -30562,7 +30562,7 @@
         <v>49</v>
       </c>
       <c r="F989" s="8">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G989" s="8" t="s">
         <v>11</v>
@@ -30585,7 +30585,7 @@
         <v>49</v>
       </c>
       <c r="F990" s="6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G990" s="6" t="s">
         <v>11</v>
@@ -30608,7 +30608,7 @@
         <v>49</v>
       </c>
       <c r="F991" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G991" s="8" t="s">
         <v>11</v>
@@ -30631,7 +30631,7 @@
         <v>49</v>
       </c>
       <c r="F992" s="6">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G992" s="6" t="s">
         <v>11</v>
@@ -30677,7 +30677,7 @@
         <v>49</v>
       </c>
       <c r="F994" s="6">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G994" s="6" t="s">
         <v>11</v>
@@ -30723,7 +30723,7 @@
         <v>49</v>
       </c>
       <c r="F996" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G996" s="6" t="s">
         <v>11</v>
@@ -30746,7 +30746,7 @@
         <v>49</v>
       </c>
       <c r="F997" s="8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G997" s="8" t="s">
         <v>11</v>
@@ -30792,7 +30792,7 @@
         <v>49</v>
       </c>
       <c r="F999" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G999" s="8" t="s">
         <v>11</v>
@@ -30815,7 +30815,7 @@
         <v>49</v>
       </c>
       <c r="F1000" s="6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G1000" s="6" t="s">
         <v>11</v>
@@ -30838,7 +30838,7 @@
         <v>49</v>
       </c>
       <c r="F1001" s="8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G1001" s="8" t="s">
         <v>11</v>
@@ -30861,7 +30861,7 @@
         <v>49</v>
       </c>
       <c r="F1002" s="6">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G1002" s="6" t="s">
         <v>11</v>
@@ -30884,7 +30884,7 @@
         <v>49</v>
       </c>
       <c r="F1003" s="8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G1003" s="8" t="s">
         <v>11</v>
@@ -30907,7 +30907,7 @@
         <v>49</v>
       </c>
       <c r="F1004" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1004" s="6" t="s">
         <v>11</v>
@@ -30930,7 +30930,7 @@
         <v>49</v>
       </c>
       <c r="F1005" s="8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G1005" s="8" t="s">
         <v>11</v>
@@ -30953,7 +30953,7 @@
         <v>49</v>
       </c>
       <c r="F1006" s="6">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G1006" s="6" t="s">
         <v>11</v>
@@ -30976,7 +30976,7 @@
         <v>49</v>
       </c>
       <c r="F1007" s="8">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G1007" s="8" t="s">
         <v>11</v>
@@ -30999,7 +30999,7 @@
         <v>49</v>
       </c>
       <c r="F1008" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1008" s="6" t="s">
         <v>11</v>
@@ -31068,7 +31068,7 @@
         <v>49</v>
       </c>
       <c r="F1011" s="8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G1011" s="8" t="s">
         <v>11</v>
@@ -31091,7 +31091,7 @@
         <v>49</v>
       </c>
       <c r="F1012" s="6">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G1012" s="6" t="s">
         <v>11</v>
@@ -31114,7 +31114,7 @@
         <v>49</v>
       </c>
       <c r="F1013" s="8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G1013" s="8" t="s">
         <v>11</v>
@@ -31183,7 +31183,7 @@
         <v>49</v>
       </c>
       <c r="F1016" s="6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G1016" s="6" t="s">
         <v>11</v>
@@ -31206,7 +31206,7 @@
         <v>49</v>
       </c>
       <c r="F1017" s="8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G1017" s="8" t="s">
         <v>11</v>
@@ -31229,7 +31229,7 @@
         <v>49</v>
       </c>
       <c r="F1018" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1018" s="6" t="s">
         <v>11</v>
@@ -31252,7 +31252,7 @@
         <v>49</v>
       </c>
       <c r="F1019" s="8">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G1019" s="8" t="s">
         <v>11</v>
@@ -31275,7 +31275,7 @@
         <v>49</v>
       </c>
       <c r="F1020" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G1020" s="6" t="s">
         <v>11</v>
@@ -31298,7 +31298,7 @@
         <v>49</v>
       </c>
       <c r="F1021" s="8">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G1021" s="8" t="s">
         <v>11</v>
@@ -31321,7 +31321,7 @@
         <v>49</v>
       </c>
       <c r="F1022" s="6">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G1022" s="6" t="s">
         <v>11</v>
@@ -31344,7 +31344,7 @@
         <v>49</v>
       </c>
       <c r="F1023" s="8">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G1023" s="8" t="s">
         <v>11</v>
@@ -31367,7 +31367,7 @@
         <v>49</v>
       </c>
       <c r="F1024" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1024" s="6" t="s">
         <v>11</v>
@@ -31390,7 +31390,7 @@
         <v>49</v>
       </c>
       <c r="F1025" s="8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G1025" s="8" t="s">
         <v>11</v>
@@ -31413,7 +31413,7 @@
         <v>49</v>
       </c>
       <c r="F1026" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G1026" s="6" t="s">
         <v>11</v>
@@ -31436,7 +31436,7 @@
         <v>49</v>
       </c>
       <c r="F1027" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1027" s="8" t="s">
         <v>11</v>
@@ -31459,7 +31459,7 @@
         <v>49</v>
       </c>
       <c r="F1028" s="6">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G1028" s="6" t="s">
         <v>11</v>
@@ -31482,7 +31482,7 @@
         <v>49</v>
       </c>
       <c r="F1029" s="8">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="G1029" s="8" t="s">
         <v>11</v>
@@ -31505,7 +31505,7 @@
         <v>49</v>
       </c>
       <c r="F1030" s="6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G1030" s="6" t="s">
         <v>11</v>
@@ -31528,7 +31528,7 @@
         <v>49</v>
       </c>
       <c r="F1031" s="8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G1031" s="8" t="s">
         <v>11</v>
@@ -31551,7 +31551,7 @@
         <v>49</v>
       </c>
       <c r="F1032" s="6">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G1032" s="6" t="s">
         <v>11</v>
@@ -31574,7 +31574,7 @@
         <v>49</v>
       </c>
       <c r="F1033" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G1033" s="8" t="s">
         <v>11</v>
@@ -31620,7 +31620,7 @@
         <v>49</v>
       </c>
       <c r="F1035" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G1035" s="8" t="s">
         <v>11</v>
@@ -31666,7 +31666,7 @@
         <v>49</v>
       </c>
       <c r="F1037" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G1037" s="8" t="s">
         <v>11</v>
@@ -31689,7 +31689,7 @@
         <v>49</v>
       </c>
       <c r="F1038" s="6">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G1038" s="6" t="s">
         <v>11</v>
@@ -31735,7 +31735,7 @@
         <v>49</v>
       </c>
       <c r="F1040" s="6">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G1040" s="6" t="s">
         <v>11</v>
@@ -31758,7 +31758,7 @@
         <v>49</v>
       </c>
       <c r="F1041" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1041" s="8" t="s">
         <v>11</v>
@@ -31781,7 +31781,7 @@
         <v>49</v>
       </c>
       <c r="F1042" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1042" s="6" t="s">
         <v>11</v>
@@ -31804,7 +31804,7 @@
         <v>49</v>
       </c>
       <c r="F1043" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1043" s="8" t="s">
         <v>11</v>
@@ -31827,7 +31827,7 @@
         <v>49</v>
       </c>
       <c r="F1044" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G1044" s="6" t="s">
         <v>11</v>
@@ -31850,7 +31850,7 @@
         <v>49</v>
       </c>
       <c r="F1045" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1045" s="8" t="s">
         <v>11</v>
@@ -31873,7 +31873,7 @@
         <v>49</v>
       </c>
       <c r="F1046" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G1046" s="6" t="s">
         <v>11</v>
@@ -31896,7 +31896,7 @@
         <v>49</v>
       </c>
       <c r="F1047" s="8">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G1047" s="8" t="s">
         <v>11</v>
@@ -31919,7 +31919,7 @@
         <v>49</v>
       </c>
       <c r="F1048" s="6">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G1048" s="6" t="s">
         <v>11</v>
@@ -31942,7 +31942,7 @@
         <v>49</v>
       </c>
       <c r="F1049" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1049" s="8" t="s">
         <v>11</v>
@@ -31965,7 +31965,7 @@
         <v>49</v>
       </c>
       <c r="F1050" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1050" s="6" t="s">
         <v>11</v>
@@ -31988,7 +31988,7 @@
         <v>49</v>
       </c>
       <c r="F1051" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1051" s="8" t="s">
         <v>11</v>
@@ -32011,7 +32011,7 @@
         <v>49</v>
       </c>
       <c r="F1052" s="6">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G1052" s="6" t="s">
         <v>11</v>
@@ -32034,7 +32034,7 @@
         <v>49</v>
       </c>
       <c r="F1053" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1053" s="8" t="s">
         <v>11</v>
@@ -32080,7 +32080,7 @@
         <v>49</v>
       </c>
       <c r="F1055" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G1055" s="8" t="s">
         <v>11</v>
@@ -32103,7 +32103,7 @@
         <v>49</v>
       </c>
       <c r="F1056" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1056" s="6" t="s">
         <v>11</v>
@@ -32126,7 +32126,7 @@
         <v>49</v>
       </c>
       <c r="F1057" s="8">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="G1057" s="8" t="s">
         <v>11</v>
@@ -32195,7 +32195,7 @@
         <v>49</v>
       </c>
       <c r="F1060" s="6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G1060" s="6" t="s">
         <v>11</v>
@@ -32218,7 +32218,7 @@
         <v>49</v>
       </c>
       <c r="F1061" s="8">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G1061" s="8" t="s">
         <v>11</v>
@@ -32241,7 +32241,7 @@
         <v>49</v>
       </c>
       <c r="F1062" s="6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G1062" s="6" t="s">
         <v>11</v>
@@ -32264,7 +32264,7 @@
         <v>49</v>
       </c>
       <c r="F1063" s="8">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G1063" s="8" t="s">
         <v>11</v>
@@ -32287,7 +32287,7 @@
         <v>49</v>
       </c>
       <c r="F1064" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1064" s="6" t="s">
         <v>11</v>
@@ -32310,7 +32310,7 @@
         <v>49</v>
       </c>
       <c r="F1065" s="8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1065" s="8" t="s">
         <v>11</v>
@@ -32333,7 +32333,7 @@
         <v>49</v>
       </c>
       <c r="F1066" s="6">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G1066" s="6" t="s">
         <v>11</v>
@@ -32356,7 +32356,7 @@
         <v>49</v>
       </c>
       <c r="F1067" s="8">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="G1067" s="8" t="s">
         <v>11</v>
@@ -32379,7 +32379,7 @@
         <v>49</v>
       </c>
       <c r="F1068" s="6">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G1068" s="6" t="s">
         <v>11</v>
@@ -32402,7 +32402,7 @@
         <v>49</v>
       </c>
       <c r="F1069" s="8">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G1069" s="8" t="s">
         <v>11</v>
@@ -32448,7 +32448,7 @@
         <v>49</v>
       </c>
       <c r="F1071" s="8">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G1071" s="8" t="s">
         <v>11</v>
@@ -32471,7 +32471,7 @@
         <v>49</v>
       </c>
       <c r="F1072" s="6">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G1072" s="6" t="s">
         <v>11</v>
@@ -32494,7 +32494,7 @@
         <v>49</v>
       </c>
       <c r="F1073" s="8">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G1073" s="8" t="s">
         <v>11</v>
@@ -32517,7 +32517,7 @@
         <v>49</v>
       </c>
       <c r="F1074" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G1074" s="6" t="s">
         <v>11</v>
@@ -32540,7 +32540,7 @@
         <v>49</v>
       </c>
       <c r="F1075" s="8">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G1075" s="8" t="s">
         <v>11</v>
@@ -32563,7 +32563,7 @@
         <v>49</v>
       </c>
       <c r="F1076" s="6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G1076" s="6" t="s">
         <v>11</v>
@@ -32586,7 +32586,7 @@
         <v>49</v>
       </c>
       <c r="F1077" s="8">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G1077" s="8" t="s">
         <v>11</v>
@@ -32609,7 +32609,7 @@
         <v>49</v>
       </c>
       <c r="F1078" s="6">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G1078" s="6" t="s">
         <v>11</v>
@@ -32632,7 +32632,7 @@
         <v>49</v>
       </c>
       <c r="F1079" s="8">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G1079" s="8" t="s">
         <v>11</v>
@@ -32655,7 +32655,7 @@
         <v>49</v>
       </c>
       <c r="F1080" s="6">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G1080" s="6" t="s">
         <v>11</v>
@@ -32678,7 +32678,7 @@
         <v>49</v>
       </c>
       <c r="F1081" s="8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G1081" s="8" t="s">
         <v>11</v>
@@ -32747,7 +32747,7 @@
         <v>49</v>
       </c>
       <c r="F1084" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1084" s="6" t="s">
         <v>11</v>
@@ -32770,7 +32770,7 @@
         <v>49</v>
       </c>
       <c r="F1085" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1085" s="8" t="s">
         <v>11</v>
@@ -32793,7 +32793,7 @@
         <v>49</v>
       </c>
       <c r="F1086" s="6">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G1086" s="6" t="s">
         <v>11</v>
@@ -32816,7 +32816,7 @@
         <v>49</v>
       </c>
       <c r="F1087" s="8">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G1087" s="8" t="s">
         <v>11</v>
@@ -32839,7 +32839,7 @@
         <v>49</v>
       </c>
       <c r="F1088" s="6">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G1088" s="6" t="s">
         <v>11</v>
@@ -32862,7 +32862,7 @@
         <v>49</v>
       </c>
       <c r="F1089" s="8">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G1089" s="8" t="s">
         <v>11</v>
@@ -32885,7 +32885,7 @@
         <v>49</v>
       </c>
       <c r="F1090" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G1090" s="6" t="s">
         <v>11</v>
@@ -32908,7 +32908,7 @@
         <v>49</v>
       </c>
       <c r="F1091" s="8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G1091" s="8" t="s">
         <v>11</v>
@@ -32931,7 +32931,7 @@
         <v>49</v>
       </c>
       <c r="F1092" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1092" s="6" t="s">
         <v>11</v>
@@ -32954,7 +32954,7 @@
         <v>49</v>
       </c>
       <c r="F1093" s="8">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G1093" s="8" t="s">
         <v>11</v>
@@ -33000,7 +33000,7 @@
         <v>49</v>
       </c>
       <c r="F1095" s="8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G1095" s="8" t="s">
         <v>11</v>
@@ -33023,7 +33023,7 @@
         <v>49</v>
       </c>
       <c r="F1096" s="6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G1096" s="6" t="s">
         <v>11</v>
@@ -33046,7 +33046,7 @@
         <v>49</v>
       </c>
       <c r="F1097" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G1097" s="8" t="s">
         <v>11</v>
@@ -33069,7 +33069,7 @@
         <v>49</v>
       </c>
       <c r="F1098" s="6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G1098" s="6" t="s">
         <v>11</v>
@@ -33092,7 +33092,7 @@
         <v>49</v>
       </c>
       <c r="F1099" s="8">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G1099" s="8" t="s">
         <v>11</v>
@@ -33115,7 +33115,7 @@
         <v>49</v>
       </c>
       <c r="F1100" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1100" s="6" t="s">
         <v>11</v>
@@ -33138,7 +33138,7 @@
         <v>49</v>
       </c>
       <c r="F1101" s="8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1101" s="8" t="s">
         <v>11</v>
@@ -33161,7 +33161,7 @@
         <v>49</v>
       </c>
       <c r="F1102" s="6">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G1102" s="6" t="s">
         <v>11</v>
@@ -33184,7 +33184,7 @@
         <v>49</v>
       </c>
       <c r="F1103" s="8">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G1103" s="8" t="s">
         <v>11</v>
@@ -33207,7 +33207,7 @@
         <v>49</v>
       </c>
       <c r="F1104" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1104" s="6" t="s">
         <v>11</v>
@@ -33230,7 +33230,7 @@
         <v>49</v>
       </c>
       <c r="F1105" s="8">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G1105" s="8" t="s">
         <v>11</v>
@@ -33253,7 +33253,7 @@
         <v>49</v>
       </c>
       <c r="F1106" s="6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G1106" s="6" t="s">
         <v>11</v>
@@ -33322,7 +33322,7 @@
         <v>49</v>
       </c>
       <c r="F1109" s="8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G1109" s="8" t="s">
         <v>11</v>
@@ -33345,7 +33345,7 @@
         <v>49</v>
       </c>
       <c r="F1110" s="6">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G1110" s="6" t="s">
         <v>11</v>
@@ -33391,7 +33391,7 @@
         <v>49</v>
       </c>
       <c r="F1112" s="6">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G1112" s="6" t="s">
         <v>11</v>
@@ -33400,6 +33400,6 @@
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>